--- a/ressources/tableaux-de-travail/GT_Dessertes_Tab_PointsEau.xlsx
+++ b/ressources/tableaux-de-travail/GT_Dessertes_Tab_PointsEau.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ignf.sharepoint.com/sites/Naviforest/Documents partages/General/Tranche 3/4. Standard Dessertes en forêt  Transport de bois et DFCI/Tableaux de travail/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WS\zz_telechargement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="104" documentId="8_{6A13F8FB-EDCF-4B90-9821-EE5A68D046D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6C59258A-A92B-42AE-BE89-9315FE06B9AB}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F1BCF877-EF07-4148-8B00-E307556AB81E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19090" yWindow="-140" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="table_v1" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="135">
   <si>
     <t>Statut de l'élément pour la v2 du standard Dessertes</t>
   </si>
@@ -462,13 +462,25 @@
   </si>
   <si>
     <t>question/proposition d'évolution  27/11/2025</t>
+  </si>
+  <si>
+    <t>validé par le GT</t>
+  </si>
+  <si>
+    <t>Pas de problématiques, on peut garder tel que le standard AFIGEO</t>
+  </si>
+  <si>
+    <t>Réponse/commentaire fait pendant le GT du 16/01/2026</t>
+  </si>
+  <si>
+    <t>ok</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -541,8 +553,19 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -583,6 +606,12 @@
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor rgb="FFD9D9D9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -651,7 +680,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -662,9 +691,6 @@
     <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -684,20 +710,71 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -707,53 +784,44 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1091,60 +1159,60 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85754B1D-2531-463F-8465-85A5AC0ED493}">
   <dimension ref="A1:R30"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.75" defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.75" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="30.83203125" customWidth="1"/>
+    <col min="1" max="1" width="30.875" customWidth="1"/>
     <col min="2" max="2" width="29.75" customWidth="1"/>
     <col min="3" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="19.58203125" customWidth="1"/>
-    <col min="5" max="5" width="13.58203125" customWidth="1"/>
+    <col min="4" max="4" width="19.625" customWidth="1"/>
+    <col min="5" max="5" width="13.625" customWidth="1"/>
     <col min="6" max="6" width="26.25" customWidth="1"/>
-    <col min="7" max="7" width="21.1640625" customWidth="1"/>
-    <col min="8" max="8" width="36.1640625" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="13.83203125" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="15.58203125" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="21.125" customWidth="1"/>
+    <col min="8" max="8" width="36.125" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="13.875" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="15.625" hidden="1" customWidth="1"/>
     <col min="11" max="11" width="25.75" hidden="1" customWidth="1"/>
     <col min="12" max="12" width="20" hidden="1" customWidth="1"/>
-    <col min="13" max="13" width="16.58203125" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="19.58203125" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="23.83203125" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="16.625" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="19.625" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="23.875" hidden="1" customWidth="1"/>
     <col min="16" max="16" width="19.75" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.58203125" customWidth="1"/>
-    <col min="18" max="18" width="16.58203125" customWidth="1"/>
+    <col min="17" max="17" width="15.625" customWidth="1"/>
+    <col min="18" max="18" width="16.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="31" customHeight="1">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:18" ht="30.95" customHeight="1">
+      <c r="A1" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="31" t="s">
         <v>69</v>
       </c>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="23" t="s">
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="4"/>
-      <c r="J1" s="18" t="s">
+      <c r="I1" s="33"/>
+      <c r="J1" s="34" t="s">
         <v>129</v>
       </c>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
-      <c r="O1" s="20"/>
-      <c r="P1" s="13" t="s">
+      <c r="K1" s="35"/>
+      <c r="L1" s="35"/>
+      <c r="M1" s="35"/>
+      <c r="N1" s="35"/>
+      <c r="O1" s="36"/>
+      <c r="P1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="Q1" s="22"/>
-      <c r="R1" s="22"/>
+      <c r="Q1" s="17"/>
+      <c r="R1" s="17"/>
     </row>
     <row r="2" spans="1:18" ht="95.25" customHeight="1">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="12" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -1171,25 +1239,25 @@
       <c r="I2" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="J2" s="21" t="s">
+      <c r="J2" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="K2" s="21" t="s">
+      <c r="K2" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="L2" s="21" t="s">
+      <c r="L2" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="M2" s="21" t="s">
+      <c r="M2" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="N2" s="21" t="s">
+      <c r="N2" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="O2" s="21" t="s">
+      <c r="O2" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="P2" s="15" t="s">
+      <c r="P2" s="13" t="s">
         <v>3</v>
       </c>
       <c r="Q2" s="3" t="s">
@@ -1198,900 +1266,900 @@
       <c r="R2" s="3"/>
     </row>
     <row r="3" spans="1:18" ht="60" customHeight="1">
-      <c r="A3" s="26" t="s">
+      <c r="A3" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="B3" s="27" t="s">
+      <c r="B3" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="C3" s="27" t="s">
+      <c r="C3" s="21" t="s">
         <v>16</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="E3" s="28"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="H3" s="7" t="s">
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
+      <c r="G3" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="H3" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="I3" s="9"/>
-      <c r="J3" s="27"/>
-      <c r="K3" s="9"/>
-      <c r="L3" s="9"/>
-      <c r="M3" s="9"/>
-      <c r="N3" s="9"/>
-      <c r="O3" s="9"/>
-      <c r="P3" s="9"/>
-      <c r="Q3" s="8"/>
-      <c r="R3" s="8"/>
-    </row>
-    <row r="4" spans="1:18" ht="87">
-      <c r="A4" s="9" t="s">
+      <c r="I3" s="8"/>
+      <c r="J3" s="21"/>
+      <c r="K3" s="8"/>
+      <c r="L3" s="8"/>
+      <c r="M3" s="8"/>
+      <c r="N3" s="8"/>
+      <c r="O3" s="8"/>
+      <c r="P3" s="8"/>
+      <c r="Q3" s="7"/>
+      <c r="R3" s="7"/>
+    </row>
+    <row r="4" spans="1:18" ht="90">
+      <c r="A4" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="B4" s="27" t="s">
+      <c r="B4" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="C4" s="27" t="s">
+      <c r="C4" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="27" t="s">
+      <c r="D4" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="H4" s="30" t="s">
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="H4" s="24" t="s">
         <v>115</v>
       </c>
-      <c r="I4" s="9"/>
-      <c r="J4" s="27"/>
-      <c r="K4" s="9"/>
-      <c r="L4" s="9"/>
-      <c r="M4" s="9"/>
-      <c r="N4" s="9"/>
-      <c r="O4" s="9"/>
-      <c r="P4" s="9"/>
-      <c r="Q4" s="9"/>
-      <c r="R4" s="9"/>
-    </row>
-    <row r="5" spans="1:18" ht="72.5">
-      <c r="A5" s="9" t="s">
+      <c r="I4" s="8"/>
+      <c r="J4" s="21"/>
+      <c r="K4" s="8"/>
+      <c r="L4" s="8"/>
+      <c r="M4" s="8"/>
+      <c r="N4" s="8"/>
+      <c r="O4" s="8"/>
+      <c r="P4" s="8"/>
+      <c r="Q4" s="8"/>
+      <c r="R4" s="8"/>
+    </row>
+    <row r="5" spans="1:18" ht="75">
+      <c r="A5" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="B5" s="27" t="s">
+      <c r="B5" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="C5" s="27" t="s">
+      <c r="C5" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="27" t="s">
+      <c r="D5" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="H5" s="30" t="s">
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="H5" s="24" t="s">
         <v>111</v>
       </c>
-      <c r="I5" s="9"/>
-      <c r="J5" s="27"/>
-      <c r="K5" s="9"/>
-      <c r="L5" s="9"/>
-      <c r="M5" s="9"/>
-      <c r="N5" s="9"/>
-      <c r="O5" s="9"/>
-      <c r="P5" s="9"/>
-      <c r="Q5" s="9"/>
-      <c r="R5" s="9"/>
-    </row>
-    <row r="6" spans="1:18" ht="15.5">
-      <c r="A6" s="9" t="s">
+      <c r="I5" s="8"/>
+      <c r="J5" s="21"/>
+      <c r="K5" s="8"/>
+      <c r="L5" s="8"/>
+      <c r="M5" s="8"/>
+      <c r="N5" s="8"/>
+      <c r="O5" s="8"/>
+      <c r="P5" s="8"/>
+      <c r="Q5" s="8"/>
+      <c r="R5" s="8"/>
+    </row>
+    <row r="6" spans="1:18" ht="15.75">
+      <c r="A6" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="B6" s="27" t="s">
+      <c r="B6" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="C6" s="27" t="s">
+      <c r="C6" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="27" t="s">
+      <c r="D6" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="H6" s="31" t="s">
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="H6" s="25" t="s">
         <v>112</v>
       </c>
-      <c r="I6" s="10"/>
-      <c r="J6" s="27"/>
-      <c r="K6" s="10"/>
-      <c r="L6" s="10"/>
-      <c r="M6" s="10"/>
-      <c r="N6" s="10"/>
-      <c r="O6" s="10"/>
-      <c r="P6" s="10"/>
-      <c r="Q6" s="10"/>
-      <c r="R6" s="10"/>
-    </row>
-    <row r="7" spans="1:18" ht="43.5">
-      <c r="A7" s="9" t="s">
+      <c r="I6" s="9"/>
+      <c r="J6" s="21"/>
+      <c r="K6" s="9"/>
+      <c r="L6" s="9"/>
+      <c r="M6" s="9"/>
+      <c r="N6" s="9"/>
+      <c r="O6" s="9"/>
+      <c r="P6" s="9"/>
+      <c r="Q6" s="9"/>
+      <c r="R6" s="9"/>
+    </row>
+    <row r="7" spans="1:18" ht="45">
+      <c r="A7" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="B7" s="27" t="s">
+      <c r="B7" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="C7" s="27" t="s">
+      <c r="C7" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="27" t="s">
+      <c r="D7" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="H7" s="32" t="s">
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="H7" s="26" t="s">
         <v>113</v>
       </c>
-      <c r="I7" s="9"/>
-      <c r="J7" s="27"/>
-      <c r="K7" s="9"/>
-      <c r="L7" s="9"/>
-      <c r="M7" s="33"/>
-      <c r="N7" s="9"/>
-      <c r="O7" s="9"/>
-      <c r="P7" s="9"/>
-      <c r="Q7" s="8"/>
-      <c r="R7" s="8"/>
-    </row>
-    <row r="8" spans="1:18" ht="101.5">
-      <c r="A8" s="9" t="s">
+      <c r="I7" s="8"/>
+      <c r="J7" s="21"/>
+      <c r="K7" s="8"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="27"/>
+      <c r="N7" s="8"/>
+      <c r="O7" s="8"/>
+      <c r="P7" s="8"/>
+      <c r="Q7" s="7"/>
+      <c r="R7" s="7"/>
+    </row>
+    <row r="8" spans="1:18" ht="105">
+      <c r="A8" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="B8" s="27" t="s">
+      <c r="B8" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="C8" s="27" t="s">
+      <c r="C8" s="21" t="s">
         <v>16</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9" t="s">
+      <c r="E8" s="8"/>
+      <c r="F8" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="G8" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="H8" s="30" t="s">
+      <c r="G8" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="H8" s="24" t="s">
         <v>114</v>
       </c>
-      <c r="I8" s="9"/>
-      <c r="J8" s="27"/>
-      <c r="K8" s="9"/>
-      <c r="L8" s="9"/>
-      <c r="M8" s="9"/>
-      <c r="N8" s="9"/>
-      <c r="O8" s="9"/>
-      <c r="P8" s="9"/>
-      <c r="Q8" s="8"/>
-      <c r="R8" s="8"/>
-    </row>
-    <row r="9" spans="1:18" ht="29">
-      <c r="A9" s="9" t="s">
+      <c r="I8" s="8"/>
+      <c r="J8" s="21"/>
+      <c r="K8" s="8"/>
+      <c r="L8" s="8"/>
+      <c r="M8" s="8"/>
+      <c r="N8" s="8"/>
+      <c r="O8" s="8"/>
+      <c r="P8" s="8"/>
+      <c r="Q8" s="7"/>
+      <c r="R8" s="7"/>
+    </row>
+    <row r="9" spans="1:18" ht="30">
+      <c r="A9" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="B9" s="27" t="s">
+      <c r="B9" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="C9" s="27" t="s">
+      <c r="C9" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="27" t="s">
+      <c r="D9" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="H9" s="34" t="s">
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+      <c r="G9" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="H9" s="28" t="s">
         <v>116</v>
       </c>
-      <c r="I9" s="9"/>
-      <c r="J9" s="27"/>
-      <c r="K9" s="9"/>
-      <c r="L9" s="9"/>
-      <c r="M9" s="9"/>
-      <c r="N9" s="9"/>
-      <c r="O9" s="9"/>
-      <c r="P9" s="9"/>
-      <c r="Q9" s="8"/>
-      <c r="R9" s="8"/>
-    </row>
-    <row r="10" spans="1:18" ht="84">
-      <c r="A10" s="9" t="s">
+      <c r="I9" s="8"/>
+      <c r="J9" s="21"/>
+      <c r="K9" s="8"/>
+      <c r="L9" s="8"/>
+      <c r="M9" s="8"/>
+      <c r="N9" s="8"/>
+      <c r="O9" s="8"/>
+      <c r="P9" s="8"/>
+      <c r="Q9" s="7"/>
+      <c r="R9" s="7"/>
+    </row>
+    <row r="10" spans="1:18" ht="85.5">
+      <c r="A10" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="B10" s="27" t="s">
+      <c r="B10" s="21" t="s">
         <v>49</v>
       </c>
-      <c r="C10" s="27" t="s">
+      <c r="C10" s="21" t="s">
         <v>33</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9" t="s">
+      <c r="E10" s="8"/>
+      <c r="F10" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="G10" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="H10" s="32" t="s">
+      <c r="G10" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="H10" s="26" t="s">
         <v>117</v>
       </c>
-      <c r="I10" s="9"/>
-      <c r="J10" s="27"/>
-      <c r="K10" s="9"/>
-      <c r="L10" s="9"/>
-      <c r="M10" s="9"/>
-      <c r="N10" s="9"/>
-      <c r="O10" s="9"/>
-      <c r="P10" s="9"/>
-      <c r="Q10" s="8"/>
-      <c r="R10" s="8"/>
-    </row>
-    <row r="11" spans="1:18" ht="29">
-      <c r="A11" s="9" t="s">
+      <c r="I10" s="8"/>
+      <c r="J10" s="21"/>
+      <c r="K10" s="8"/>
+      <c r="L10" s="8"/>
+      <c r="M10" s="8"/>
+      <c r="N10" s="8"/>
+      <c r="O10" s="8"/>
+      <c r="P10" s="8"/>
+      <c r="Q10" s="7"/>
+      <c r="R10" s="7"/>
+    </row>
+    <row r="11" spans="1:18" ht="30">
+      <c r="A11" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="B11" s="27" t="s">
+      <c r="B11" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="C11" s="27" t="s">
+      <c r="C11" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="D11" s="27" t="s">
+      <c r="D11" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="H11" s="32" t="s">
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="H11" s="26" t="s">
         <v>117</v>
       </c>
-      <c r="I11" s="9"/>
-      <c r="J11" s="27"/>
-      <c r="K11" s="9"/>
-      <c r="L11" s="9"/>
-      <c r="M11" s="9"/>
-      <c r="N11" s="9"/>
-      <c r="O11" s="9"/>
-      <c r="P11" s="9"/>
-      <c r="Q11" s="8"/>
-      <c r="R11" s="8"/>
-    </row>
-    <row r="12" spans="1:18" ht="58">
-      <c r="A12" s="9" t="s">
+      <c r="I11" s="8"/>
+      <c r="J11" s="21"/>
+      <c r="K11" s="8"/>
+      <c r="L11" s="8"/>
+      <c r="M11" s="8"/>
+      <c r="N11" s="8"/>
+      <c r="O11" s="8"/>
+      <c r="P11" s="8"/>
+      <c r="Q11" s="7"/>
+      <c r="R11" s="7"/>
+    </row>
+    <row r="12" spans="1:18" ht="60">
+      <c r="A12" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="B12" s="27" t="s">
+      <c r="B12" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="C12" s="27" t="s">
+      <c r="C12" s="21" t="s">
         <v>16</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9" t="s">
+      <c r="E12" s="8"/>
+      <c r="F12" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="G12" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="H12" s="32" t="s">
+      <c r="G12" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="H12" s="26" t="s">
         <v>118</v>
       </c>
-      <c r="I12" s="9"/>
-      <c r="J12" s="27"/>
-      <c r="K12" s="9"/>
-      <c r="L12" s="9"/>
-      <c r="M12" s="9"/>
-      <c r="N12" s="9"/>
-      <c r="O12" s="9"/>
-      <c r="P12" s="9"/>
-      <c r="Q12" s="8"/>
-      <c r="R12" s="8"/>
-    </row>
-    <row r="13" spans="1:18" ht="70">
-      <c r="A13" s="9" t="s">
+      <c r="I12" s="8"/>
+      <c r="J12" s="21"/>
+      <c r="K12" s="8"/>
+      <c r="L12" s="8"/>
+      <c r="M12" s="8"/>
+      <c r="N12" s="8"/>
+      <c r="O12" s="8"/>
+      <c r="P12" s="8"/>
+      <c r="Q12" s="7"/>
+      <c r="R12" s="7"/>
+    </row>
+    <row r="13" spans="1:18" ht="71.25">
+      <c r="A13" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="B13" s="27" t="s">
+      <c r="B13" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="C13" s="27" t="s">
+      <c r="C13" s="21" t="s">
         <v>16</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9" t="s">
+      <c r="E13" s="8"/>
+      <c r="F13" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="G13" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="H13" s="34" t="s">
+      <c r="G13" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="H13" s="28" t="s">
         <v>120</v>
       </c>
-      <c r="I13" s="9"/>
-      <c r="J13" s="27"/>
-      <c r="K13" s="9"/>
-      <c r="L13" s="9"/>
-      <c r="M13" s="9"/>
-      <c r="N13" s="9"/>
-      <c r="O13" s="9"/>
-      <c r="P13" s="9"/>
-      <c r="Q13" s="9"/>
-      <c r="R13" s="9"/>
-    </row>
-    <row r="14" spans="1:18" ht="29">
-      <c r="A14" s="9" t="s">
+      <c r="I13" s="8"/>
+      <c r="J13" s="21"/>
+      <c r="K13" s="8"/>
+      <c r="L13" s="8"/>
+      <c r="M13" s="8"/>
+      <c r="N13" s="8"/>
+      <c r="O13" s="8"/>
+      <c r="P13" s="8"/>
+      <c r="Q13" s="8"/>
+      <c r="R13" s="8"/>
+    </row>
+    <row r="14" spans="1:18" ht="30">
+      <c r="A14" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="B14" s="27" t="s">
+      <c r="B14" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="C14" s="27" t="s">
+      <c r="C14" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="D14" s="27" t="s">
+      <c r="D14" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="H14" s="32" t="s">
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="H14" s="26" t="s">
         <v>121</v>
       </c>
-      <c r="I14" s="9"/>
-      <c r="J14" s="27"/>
-      <c r="K14" s="9"/>
-      <c r="L14" s="9"/>
-      <c r="M14" s="9"/>
-      <c r="N14" s="9"/>
-      <c r="O14" s="9"/>
-      <c r="P14" s="9"/>
-      <c r="Q14" s="9"/>
-      <c r="R14" s="9"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="21"/>
+      <c r="K14" s="8"/>
+      <c r="L14" s="8"/>
+      <c r="M14" s="8"/>
+      <c r="N14" s="8"/>
+      <c r="O14" s="8"/>
+      <c r="P14" s="8"/>
+      <c r="Q14" s="8"/>
+      <c r="R14" s="8"/>
     </row>
     <row r="15" spans="1:18" ht="60.75" customHeight="1">
-      <c r="A15" s="9" t="s">
+      <c r="A15" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="B15" s="27" t="s">
+      <c r="B15" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="C15" s="27" t="s">
+      <c r="C15" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="D15" s="27" t="s">
+      <c r="D15" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="E15" s="9"/>
-      <c r="F15" s="25"/>
-      <c r="G15" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="H15" s="9" t="s">
+      <c r="E15" s="8"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="H15" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="I15" s="10"/>
-      <c r="J15" s="27"/>
-      <c r="K15" s="10"/>
-      <c r="L15" s="10"/>
-      <c r="M15" s="10"/>
-      <c r="N15" s="10"/>
-      <c r="O15" s="10"/>
-      <c r="P15" s="10"/>
-      <c r="Q15" s="10"/>
-      <c r="R15" s="10"/>
-    </row>
-    <row r="16" spans="1:18" ht="29">
-      <c r="A16" s="9" t="s">
+      <c r="I15" s="9"/>
+      <c r="J15" s="21"/>
+      <c r="K15" s="9"/>
+      <c r="L15" s="9"/>
+      <c r="M15" s="9"/>
+      <c r="N15" s="9"/>
+      <c r="O15" s="9"/>
+      <c r="P15" s="9"/>
+      <c r="Q15" s="9"/>
+      <c r="R15" s="9"/>
+    </row>
+    <row r="16" spans="1:18" ht="30">
+      <c r="A16" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="B16" s="27" t="s">
+      <c r="B16" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="C16" s="27" t="s">
+      <c r="C16" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="D16" s="27" t="s">
+      <c r="D16" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="H16" s="35" t="s">
+      <c r="E16" s="8"/>
+      <c r="F16" s="8"/>
+      <c r="G16" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="H16" s="29" t="s">
         <v>123</v>
       </c>
-      <c r="I16" s="9"/>
-      <c r="J16" s="27"/>
-      <c r="K16" s="9"/>
-      <c r="L16" s="9"/>
-      <c r="M16" s="9"/>
-      <c r="N16" s="9"/>
-      <c r="O16" s="9"/>
-      <c r="P16" s="9"/>
-      <c r="Q16" s="8"/>
-      <c r="R16" s="8"/>
+      <c r="I16" s="8"/>
+      <c r="J16" s="21"/>
+      <c r="K16" s="8"/>
+      <c r="L16" s="8"/>
+      <c r="M16" s="8"/>
+      <c r="N16" s="8"/>
+      <c r="O16" s="8"/>
+      <c r="P16" s="8"/>
+      <c r="Q16" s="7"/>
+      <c r="R16" s="7"/>
     </row>
     <row r="17" spans="1:18" ht="72.75" customHeight="1">
-      <c r="A17" s="9" t="s">
+      <c r="A17" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="B17" s="27" t="s">
+      <c r="B17" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="C17" s="27" t="s">
+      <c r="C17" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="D17" s="27" t="s">
+      <c r="D17" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="H17" s="35" t="s">
+      <c r="E17" s="8"/>
+      <c r="F17" s="8"/>
+      <c r="G17" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="H17" s="29" t="s">
         <v>123</v>
       </c>
-      <c r="I17" s="9"/>
-      <c r="J17" s="27"/>
-      <c r="K17" s="9"/>
-      <c r="L17" s="9"/>
-      <c r="M17" s="9"/>
-      <c r="N17" s="9"/>
-      <c r="O17" s="9"/>
-      <c r="P17" s="9"/>
-      <c r="Q17" s="8"/>
-      <c r="R17" s="8"/>
-    </row>
-    <row r="18" spans="1:18" ht="29">
-      <c r="A18" s="9" t="s">
+      <c r="I17" s="8"/>
+      <c r="J17" s="21"/>
+      <c r="K17" s="8"/>
+      <c r="L17" s="8"/>
+      <c r="M17" s="8"/>
+      <c r="N17" s="8"/>
+      <c r="O17" s="8"/>
+      <c r="P17" s="8"/>
+      <c r="Q17" s="7"/>
+      <c r="R17" s="7"/>
+    </row>
+    <row r="18" spans="1:18" ht="30">
+      <c r="A18" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="B18" s="27" t="s">
+      <c r="B18" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="C18" s="27" t="s">
+      <c r="C18" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="D18" s="27" t="s">
+      <c r="D18" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="H18" s="35" t="s">
+      <c r="E18" s="8"/>
+      <c r="F18" s="8"/>
+      <c r="G18" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="H18" s="29" t="s">
         <v>123</v>
       </c>
-      <c r="I18" s="9"/>
-      <c r="J18" s="27"/>
-      <c r="K18" s="9"/>
-      <c r="L18" s="9"/>
-      <c r="M18" s="9"/>
-      <c r="N18" s="9"/>
-      <c r="O18" s="9"/>
-      <c r="P18" s="9"/>
-      <c r="Q18" s="8"/>
-      <c r="R18" s="8"/>
-    </row>
-    <row r="19" spans="1:18" ht="43.5">
-      <c r="A19" s="9" t="s">
+      <c r="I18" s="8"/>
+      <c r="J18" s="21"/>
+      <c r="K18" s="8"/>
+      <c r="L18" s="8"/>
+      <c r="M18" s="8"/>
+      <c r="N18" s="8"/>
+      <c r="O18" s="8"/>
+      <c r="P18" s="8"/>
+      <c r="Q18" s="7"/>
+      <c r="R18" s="7"/>
+    </row>
+    <row r="19" spans="1:18" ht="45">
+      <c r="A19" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="B19" s="27" t="s">
+      <c r="B19" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="C19" s="27" t="s">
+      <c r="C19" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="D19" s="27" t="s">
+      <c r="D19" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="E19" s="9"/>
-      <c r="F19" s="25"/>
-      <c r="G19" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="H19" s="35" t="s">
+      <c r="E19" s="8"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="H19" s="29" t="s">
         <v>124</v>
       </c>
-      <c r="I19" s="9"/>
-      <c r="J19" s="27"/>
-      <c r="K19" s="9"/>
-      <c r="L19" s="9"/>
-      <c r="M19" s="9"/>
-      <c r="N19" s="9"/>
-      <c r="O19" s="9"/>
-      <c r="P19" s="9"/>
-      <c r="Q19" s="8"/>
-      <c r="R19" s="8"/>
-    </row>
-    <row r="20" spans="1:18" ht="15.5">
-      <c r="A20" s="9" t="s">
+      <c r="I19" s="8"/>
+      <c r="J19" s="21"/>
+      <c r="K19" s="8"/>
+      <c r="L19" s="8"/>
+      <c r="M19" s="8"/>
+      <c r="N19" s="8"/>
+      <c r="O19" s="8"/>
+      <c r="P19" s="8"/>
+      <c r="Q19" s="7"/>
+      <c r="R19" s="7"/>
+    </row>
+    <row r="20" spans="1:18" ht="15.75">
+      <c r="A20" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="B20" s="27" t="s">
+      <c r="B20" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="C20" s="27" t="s">
+      <c r="C20" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="D20" s="27" t="s">
+      <c r="D20" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="E20" s="9"/>
-      <c r="F20" s="25"/>
-      <c r="G20" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="H20" s="9" t="s">
+      <c r="E20" s="8"/>
+      <c r="F20" s="19"/>
+      <c r="G20" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="H20" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="I20" s="9"/>
-      <c r="J20" s="27"/>
-      <c r="K20" s="9"/>
-      <c r="L20" s="9"/>
-      <c r="M20" s="9"/>
-      <c r="N20" s="9"/>
-      <c r="O20" s="9"/>
-      <c r="P20" s="9"/>
-      <c r="Q20" s="8"/>
-      <c r="R20" s="8"/>
-    </row>
-    <row r="21" spans="1:18" ht="15.5">
-      <c r="A21" s="9" t="s">
+      <c r="I20" s="8"/>
+      <c r="J20" s="21"/>
+      <c r="K20" s="8"/>
+      <c r="L20" s="8"/>
+      <c r="M20" s="8"/>
+      <c r="N20" s="8"/>
+      <c r="O20" s="8"/>
+      <c r="P20" s="8"/>
+      <c r="Q20" s="7"/>
+      <c r="R20" s="7"/>
+    </row>
+    <row r="21" spans="1:18" ht="15.75">
+      <c r="A21" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="B21" s="27" t="s">
+      <c r="B21" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="C21" s="27" t="s">
+      <c r="C21" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="D21" s="27" t="s">
+      <c r="D21" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="H21" s="9"/>
-      <c r="I21" s="9"/>
-      <c r="J21" s="27"/>
-      <c r="K21" s="9"/>
-      <c r="L21" s="9"/>
-      <c r="M21" s="9"/>
-      <c r="N21" s="9"/>
-      <c r="O21" s="9"/>
-      <c r="P21" s="9"/>
-      <c r="Q21" s="8"/>
-      <c r="R21" s="8"/>
-    </row>
-    <row r="22" spans="1:18" ht="15.5">
-      <c r="A22" s="9" t="s">
+      <c r="E21" s="8"/>
+      <c r="F21" s="8"/>
+      <c r="G21" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="H21" s="8"/>
+      <c r="I21" s="8"/>
+      <c r="J21" s="21"/>
+      <c r="K21" s="8"/>
+      <c r="L21" s="8"/>
+      <c r="M21" s="8"/>
+      <c r="N21" s="8"/>
+      <c r="O21" s="8"/>
+      <c r="P21" s="8"/>
+      <c r="Q21" s="7"/>
+      <c r="R21" s="7"/>
+    </row>
+    <row r="22" spans="1:18" ht="15.75">
+      <c r="A22" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="B22" s="27" t="s">
+      <c r="B22" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="C22" s="27" t="s">
+      <c r="C22" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="D22" s="27" t="s">
+      <c r="D22" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="H22" s="9"/>
-      <c r="I22" s="9"/>
-      <c r="J22" s="27"/>
-      <c r="K22" s="9"/>
-      <c r="L22" s="9"/>
-      <c r="M22" s="9"/>
-      <c r="N22" s="9"/>
-      <c r="O22" s="9"/>
-      <c r="P22" s="9"/>
-      <c r="Q22" s="8"/>
-      <c r="R22" s="8"/>
-    </row>
-    <row r="23" spans="1:18" ht="15.5">
-      <c r="A23" s="9" t="s">
+      <c r="E22" s="8"/>
+      <c r="F22" s="8"/>
+      <c r="G22" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="H22" s="8"/>
+      <c r="I22" s="8"/>
+      <c r="J22" s="21"/>
+      <c r="K22" s="8"/>
+      <c r="L22" s="8"/>
+      <c r="M22" s="8"/>
+      <c r="N22" s="8"/>
+      <c r="O22" s="8"/>
+      <c r="P22" s="8"/>
+      <c r="Q22" s="7"/>
+      <c r="R22" s="7"/>
+    </row>
+    <row r="23" spans="1:18" ht="15.75">
+      <c r="A23" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="B23" s="27" t="s">
+      <c r="B23" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="C23" s="27" t="s">
+      <c r="C23" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="D23" s="27" t="s">
+      <c r="D23" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="H23" s="9"/>
-      <c r="I23" s="9"/>
-      <c r="J23" s="27"/>
-      <c r="K23" s="9"/>
-      <c r="L23" s="9"/>
-      <c r="M23" s="9"/>
-      <c r="N23" s="9"/>
-      <c r="O23" s="9"/>
-      <c r="P23" s="9"/>
-      <c r="Q23" s="8"/>
-      <c r="R23" s="8"/>
-    </row>
-    <row r="24" spans="1:18" ht="15.5">
-      <c r="A24" s="9" t="s">
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="H23" s="8"/>
+      <c r="I23" s="8"/>
+      <c r="J23" s="21"/>
+      <c r="K23" s="8"/>
+      <c r="L23" s="8"/>
+      <c r="M23" s="8"/>
+      <c r="N23" s="8"/>
+      <c r="O23" s="8"/>
+      <c r="P23" s="8"/>
+      <c r="Q23" s="7"/>
+      <c r="R23" s="7"/>
+    </row>
+    <row r="24" spans="1:18" ht="15.75">
+      <c r="A24" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="B24" s="27" t="s">
+      <c r="B24" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="C24" s="27" t="s">
+      <c r="C24" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="27" t="s">
+      <c r="D24" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="H24" s="9"/>
-      <c r="I24" s="9"/>
-      <c r="J24" s="27"/>
-      <c r="K24" s="9"/>
-      <c r="L24" s="9"/>
-      <c r="M24" s="9"/>
-      <c r="N24" s="9"/>
-      <c r="O24" s="9"/>
-      <c r="P24" s="9"/>
-      <c r="Q24" s="8"/>
-      <c r="R24" s="8"/>
-    </row>
-    <row r="25" spans="1:18" ht="29">
-      <c r="A25" s="9" t="s">
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
+      <c r="J24" s="21"/>
+      <c r="K24" s="8"/>
+      <c r="L24" s="8"/>
+      <c r="M24" s="8"/>
+      <c r="N24" s="8"/>
+      <c r="O24" s="8"/>
+      <c r="P24" s="8"/>
+      <c r="Q24" s="7"/>
+      <c r="R24" s="7"/>
+    </row>
+    <row r="25" spans="1:18" ht="30">
+      <c r="A25" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="B25" s="27" t="s">
+      <c r="B25" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="C25" s="27" t="s">
+      <c r="C25" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="D25" s="27" t="s">
+      <c r="D25" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="E25" s="36"/>
-      <c r="F25" s="36"/>
-      <c r="G25" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="H25" s="36"/>
-      <c r="I25" s="36"/>
-      <c r="J25" s="27"/>
-      <c r="K25" s="36"/>
-      <c r="L25" s="36"/>
-      <c r="M25" s="36"/>
-      <c r="N25" s="36"/>
-      <c r="O25" s="36"/>
-      <c r="P25" s="36"/>
-      <c r="Q25" s="17"/>
-      <c r="R25" s="17"/>
-    </row>
-    <row r="26" spans="1:18" ht="15.5">
-      <c r="A26" s="9" t="s">
+      <c r="E25" s="30"/>
+      <c r="F25" s="30"/>
+      <c r="G25" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="H25" s="30"/>
+      <c r="I25" s="30"/>
+      <c r="J25" s="21"/>
+      <c r="K25" s="30"/>
+      <c r="L25" s="30"/>
+      <c r="M25" s="30"/>
+      <c r="N25" s="30"/>
+      <c r="O25" s="30"/>
+      <c r="P25" s="30"/>
+      <c r="Q25" s="15"/>
+      <c r="R25" s="15"/>
+    </row>
+    <row r="26" spans="1:18" ht="15.75">
+      <c r="A26" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="B26" s="27" t="s">
+      <c r="B26" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="C26" s="27" t="s">
+      <c r="C26" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="D26" s="27" t="s">
+      <c r="D26" s="21" t="s">
         <v>108</v>
       </c>
-      <c r="E26" s="36"/>
-      <c r="F26" s="36" t="s">
+      <c r="E26" s="30"/>
+      <c r="F26" s="30" t="s">
         <v>109</v>
       </c>
-      <c r="G26" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="H26" s="36" t="s">
+      <c r="G26" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="H26" s="30" t="s">
         <v>126</v>
       </c>
-      <c r="I26" s="36"/>
-      <c r="J26" s="27"/>
-      <c r="K26" s="36"/>
-      <c r="L26" s="36"/>
-      <c r="M26" s="36"/>
-      <c r="N26" s="36"/>
-      <c r="O26" s="36"/>
-      <c r="P26" s="36"/>
-      <c r="Q26" s="17"/>
-      <c r="R26" s="17"/>
-    </row>
-    <row r="27" spans="1:18" ht="15.5">
-      <c r="A27" s="9" t="s">
+      <c r="I26" s="30"/>
+      <c r="J26" s="21"/>
+      <c r="K26" s="30"/>
+      <c r="L26" s="30"/>
+      <c r="M26" s="30"/>
+      <c r="N26" s="30"/>
+      <c r="O26" s="30"/>
+      <c r="P26" s="30"/>
+      <c r="Q26" s="15"/>
+      <c r="R26" s="15"/>
+    </row>
+    <row r="27" spans="1:18" ht="15.75">
+      <c r="A27" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="B27" s="27" t="s">
+      <c r="B27" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="C27" s="27" t="s">
+      <c r="C27" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="D27" s="27" t="s">
+      <c r="D27" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="E27" s="36"/>
-      <c r="F27" s="36"/>
-      <c r="G27" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="H27" s="36" t="s">
+      <c r="E27" s="30"/>
+      <c r="F27" s="30"/>
+      <c r="G27" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="H27" s="30" t="s">
         <v>127</v>
       </c>
-      <c r="I27" s="27"/>
-      <c r="J27" s="27"/>
-      <c r="K27" s="36"/>
-      <c r="L27" s="36"/>
-      <c r="M27" s="36"/>
-      <c r="N27" s="36"/>
-      <c r="O27" s="36"/>
-      <c r="P27" s="27"/>
-      <c r="Q27" s="16"/>
-      <c r="R27" s="16"/>
-    </row>
-    <row r="28" spans="1:18" ht="15.5">
-      <c r="A28" s="9" t="s">
+      <c r="I27" s="21"/>
+      <c r="J27" s="21"/>
+      <c r="K27" s="30"/>
+      <c r="L27" s="30"/>
+      <c r="M27" s="30"/>
+      <c r="N27" s="30"/>
+      <c r="O27" s="30"/>
+      <c r="P27" s="21"/>
+      <c r="Q27" s="14"/>
+      <c r="R27" s="14"/>
+    </row>
+    <row r="28" spans="1:18" ht="15.75">
+      <c r="A28" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B28" s="27" t="s">
+      <c r="B28" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="C28" s="27" t="s">
+      <c r="C28" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="D28" s="27" t="s">
+      <c r="D28" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="E28" s="27"/>
-      <c r="F28" s="27"/>
-      <c r="G28" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="H28" s="36" t="s">
+      <c r="E28" s="21"/>
+      <c r="F28" s="21"/>
+      <c r="G28" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="H28" s="30" t="s">
         <v>127</v>
       </c>
-      <c r="I28" s="27"/>
-      <c r="J28" s="27"/>
-      <c r="K28" s="27"/>
-      <c r="L28" s="27"/>
-      <c r="M28" s="27"/>
-      <c r="N28" s="27"/>
-      <c r="O28" s="27"/>
-      <c r="P28" s="27"/>
-      <c r="Q28" s="16"/>
-      <c r="R28" s="16"/>
-    </row>
-    <row r="29" spans="1:18" ht="15.5">
-      <c r="A29" s="9" t="s">
+      <c r="I28" s="21"/>
+      <c r="J28" s="21"/>
+      <c r="K28" s="21"/>
+      <c r="L28" s="21"/>
+      <c r="M28" s="21"/>
+      <c r="N28" s="21"/>
+      <c r="O28" s="21"/>
+      <c r="P28" s="21"/>
+      <c r="Q28" s="14"/>
+      <c r="R28" s="14"/>
+    </row>
+    <row r="29" spans="1:18" ht="15.75">
+      <c r="A29" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="B29" s="27" t="s">
+      <c r="B29" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="C29" s="27" t="s">
+      <c r="C29" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="D29" s="27" t="s">
+      <c r="D29" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="E29" s="27"/>
-      <c r="F29" s="27"/>
-      <c r="G29" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="H29" s="36" t="s">
+      <c r="E29" s="21"/>
+      <c r="F29" s="21"/>
+      <c r="G29" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="H29" s="30" t="s">
         <v>127</v>
       </c>
-      <c r="I29" s="27"/>
-      <c r="J29" s="27"/>
-      <c r="K29" s="27"/>
-      <c r="L29" s="27"/>
-      <c r="M29" s="27"/>
-      <c r="N29" s="27"/>
-      <c r="O29" s="27"/>
-      <c r="P29" s="27"/>
-      <c r="Q29" s="16"/>
-      <c r="R29" s="16"/>
-    </row>
-    <row r="30" spans="1:18" ht="15.5">
-      <c r="A30" s="9" t="s">
+      <c r="I29" s="21"/>
+      <c r="J29" s="21"/>
+      <c r="K29" s="21"/>
+      <c r="L29" s="21"/>
+      <c r="M29" s="21"/>
+      <c r="N29" s="21"/>
+      <c r="O29" s="21"/>
+      <c r="P29" s="21"/>
+      <c r="Q29" s="14"/>
+      <c r="R29" s="14"/>
+    </row>
+    <row r="30" spans="1:18" ht="15.75">
+      <c r="A30" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B30" s="27" t="s">
+      <c r="B30" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="C30" s="27" t="s">
+      <c r="C30" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="D30" s="27" t="s">
+      <c r="D30" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="E30" s="27"/>
-      <c r="F30" s="27"/>
-      <c r="G30" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="H30" s="36" t="s">
+      <c r="E30" s="21"/>
+      <c r="F30" s="21"/>
+      <c r="G30" s="22" t="s">
+        <v>4</v>
+      </c>
+      <c r="H30" s="30" t="s">
         <v>127</v>
       </c>
-      <c r="I30" s="27"/>
-      <c r="J30" s="27"/>
-      <c r="K30" s="27"/>
-      <c r="L30" s="27"/>
-      <c r="M30" s="27"/>
-      <c r="N30" s="27"/>
-      <c r="O30" s="27"/>
-      <c r="P30" s="27"/>
-      <c r="Q30" s="16"/>
-      <c r="R30" s="16"/>
+      <c r="I30" s="21"/>
+      <c r="J30" s="21"/>
+      <c r="K30" s="21"/>
+      <c r="L30" s="21"/>
+      <c r="M30" s="21"/>
+      <c r="N30" s="21"/>
+      <c r="O30" s="21"/>
+      <c r="P30" s="21"/>
+      <c r="Q30" s="14"/>
+      <c r="R30" s="14"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:R2" xr:uid="{85754B1D-2531-463F-8465-85A5AC0ED493}"/>
@@ -2107,49 +2175,53 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D536427B-83A6-4707-8C45-6BB4F1975BE7}">
-  <dimension ref="A1:P31"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="87" customHeight="1"/>
+  <dimension ref="A1:Q31"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.625" defaultRowHeight="87" customHeight="1"/>
   <cols>
-    <col min="1" max="3" width="10" style="24" customWidth="1"/>
-    <col min="4" max="4" width="37.9140625" style="24" customWidth="1"/>
-    <col min="5" max="5" width="10" style="24" customWidth="1"/>
-    <col min="6" max="6" width="21.1640625" style="24" customWidth="1"/>
-    <col min="7" max="7" width="10" style="24" customWidth="1"/>
-    <col min="8" max="8" width="37.4140625" style="24" customWidth="1"/>
-    <col min="9" max="16" width="10" style="24" customWidth="1"/>
-    <col min="17" max="16384" width="10.6640625" style="24"/>
+    <col min="1" max="3" width="10" style="18" customWidth="1"/>
+    <col min="4" max="4" width="62.375" style="18" customWidth="1"/>
+    <col min="5" max="5" width="10" style="18" customWidth="1"/>
+    <col min="6" max="6" width="21.125" style="18" customWidth="1"/>
+    <col min="7" max="7" width="10" style="18" customWidth="1"/>
+    <col min="8" max="8" width="59.375" style="18" customWidth="1"/>
+    <col min="9" max="9" width="36.875" style="18" customWidth="1"/>
+    <col min="10" max="10" width="24.5" style="18" customWidth="1"/>
+    <col min="11" max="16" width="10" style="18" hidden="1" customWidth="1"/>
+    <col min="17" max="17" width="15.375" style="18" customWidth="1"/>
+    <col min="18" max="16384" width="10.625" style="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="87" customHeight="1">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:17" ht="87" customHeight="1">
+      <c r="A1" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="31" t="s">
         <v>69</v>
       </c>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="23" t="s">
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="4"/>
-      <c r="J1" s="18" t="s">
+      <c r="I1" s="49"/>
+      <c r="J1" s="33"/>
+      <c r="K1" s="34" t="s">
         <v>129</v>
       </c>
-      <c r="K1" s="19"/>
-      <c r="L1" s="19"/>
-      <c r="M1" s="19"/>
-      <c r="N1" s="19"/>
-      <c r="O1" s="20"/>
-      <c r="P1" s="13" t="s">
+      <c r="L1" s="35"/>
+      <c r="M1" s="35"/>
+      <c r="N1" s="35"/>
+      <c r="O1" s="35"/>
+      <c r="P1" s="36"/>
+      <c r="Q1" s="11" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="87" customHeight="1">
-      <c r="A2" s="14" t="s">
+    <row r="2" spans="1:17" ht="87" customHeight="1">
+      <c r="A2" s="12" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -2176,907 +2248,947 @@
       <c r="I2" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="J2" s="21" t="s">
+      <c r="J2" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="K2" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="K2" s="21" t="s">
+      <c r="L2" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="L2" s="21" t="s">
+      <c r="M2" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="M2" s="21" t="s">
+      <c r="N2" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="N2" s="21" t="s">
+      <c r="O2" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="O2" s="21" t="s">
+      <c r="P2" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="P2" s="15" t="s">
+      <c r="Q2" s="13" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:16" s="29" customFormat="1" ht="98">
-      <c r="A3" s="26" t="s">
+    <row r="3" spans="1:17" s="23" customFormat="1" ht="60">
+      <c r="A3" s="37" t="s">
         <v>77</v>
       </c>
-      <c r="B3" s="27" t="s">
+      <c r="B3" s="44" t="s">
         <v>61</v>
       </c>
-      <c r="C3" s="27" t="s">
+      <c r="C3" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="38" t="s">
         <v>64</v>
       </c>
-      <c r="E3" s="28"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="H3" s="7" t="s">
+      <c r="E3" s="37"/>
+      <c r="F3" s="37"/>
+      <c r="G3" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="H3" s="37" t="s">
         <v>110</v>
       </c>
-      <c r="I3" s="9"/>
-      <c r="J3" s="27"/>
-      <c r="K3" s="9"/>
-      <c r="L3" s="9"/>
-      <c r="M3" s="9"/>
-      <c r="N3" s="9"/>
-      <c r="O3" s="9"/>
-      <c r="P3" s="9"/>
-    </row>
-    <row r="4" spans="1:16" s="29" customFormat="1" ht="87" customHeight="1">
-      <c r="A4" s="9" t="s">
+      <c r="I3" s="38" t="s">
+        <v>134</v>
+      </c>
+      <c r="J3" s="38"/>
+      <c r="K3" s="44"/>
+      <c r="L3" s="38"/>
+      <c r="M3" s="38"/>
+      <c r="N3" s="38"/>
+      <c r="O3" s="38"/>
+      <c r="P3" s="38"/>
+      <c r="Q3" s="38" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" s="23" customFormat="1" ht="87" customHeight="1">
+      <c r="A4" s="38" t="s">
         <v>78</v>
       </c>
-      <c r="B4" s="27" t="s">
+      <c r="B4" s="44" t="s">
         <v>60</v>
       </c>
-      <c r="C4" s="27" t="s">
+      <c r="C4" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="27" t="s">
+      <c r="D4" s="44" t="s">
         <v>59</v>
       </c>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9"/>
-      <c r="G4" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="H4" s="30" t="s">
+      <c r="E4" s="38"/>
+      <c r="F4" s="38"/>
+      <c r="G4" s="37" t="s">
+        <v>4</v>
+      </c>
+      <c r="H4" s="39" t="s">
         <v>115</v>
       </c>
-      <c r="I4" s="9"/>
-      <c r="J4" s="27"/>
-      <c r="K4" s="9"/>
-      <c r="L4" s="9"/>
-      <c r="M4" s="9"/>
-      <c r="N4" s="9"/>
-      <c r="O4" s="9"/>
-      <c r="P4" s="9"/>
-    </row>
-    <row r="5" spans="1:16" s="29" customFormat="1" ht="87" customHeight="1">
-      <c r="A5" s="9" t="s">
+      <c r="I4" s="39" t="s">
+        <v>132</v>
+      </c>
+      <c r="J4" s="39"/>
+      <c r="K4" s="44"/>
+      <c r="L4" s="38"/>
+      <c r="M4" s="38"/>
+      <c r="N4" s="38"/>
+      <c r="O4" s="38"/>
+      <c r="P4" s="38"/>
+      <c r="Q4" s="38" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" s="23" customFormat="1" ht="87" customHeight="1">
+      <c r="A5" s="40" t="s">
         <v>79</v>
       </c>
-      <c r="B5" s="27" t="s">
+      <c r="B5" s="45" t="s">
         <v>58</v>
       </c>
-      <c r="C5" s="27" t="s">
+      <c r="C5" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="27" t="s">
+      <c r="D5" s="45" t="s">
         <v>57</v>
       </c>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="H5" s="30" t="s">
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="41" t="s">
+        <v>4</v>
+      </c>
+      <c r="H5" s="43" t="s">
         <v>111</v>
       </c>
-      <c r="I5" s="9"/>
-      <c r="J5" s="27"/>
-      <c r="K5" s="9"/>
-      <c r="L5" s="9"/>
-      <c r="M5" s="9"/>
-      <c r="N5" s="9"/>
-      <c r="O5" s="9"/>
-      <c r="P5" s="9"/>
-    </row>
-    <row r="6" spans="1:16" s="29" customFormat="1" ht="87" customHeight="1">
-      <c r="A6" s="9" t="s">
+      <c r="I5" s="43"/>
+      <c r="J5" s="40"/>
+      <c r="K5" s="45"/>
+      <c r="L5" s="40"/>
+      <c r="M5" s="40"/>
+      <c r="N5" s="40"/>
+      <c r="O5" s="40"/>
+      <c r="P5" s="40"/>
+      <c r="Q5" s="40"/>
+    </row>
+    <row r="6" spans="1:17" s="23" customFormat="1" ht="87" customHeight="1">
+      <c r="A6" s="40" t="s">
         <v>80</v>
       </c>
-      <c r="B6" s="27" t="s">
+      <c r="B6" s="45" t="s">
         <v>56</v>
       </c>
-      <c r="C6" s="27" t="s">
+      <c r="C6" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="27" t="s">
+      <c r="D6" s="45" t="s">
         <v>55</v>
       </c>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="H6" s="31" t="s">
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="41" t="s">
+        <v>4</v>
+      </c>
+      <c r="H6" s="40" t="s">
         <v>112</v>
       </c>
-      <c r="I6" s="10"/>
-      <c r="J6" s="27"/>
-      <c r="K6" s="10"/>
-      <c r="L6" s="10"/>
-      <c r="M6" s="10"/>
-      <c r="N6" s="10"/>
-      <c r="O6" s="10"/>
-      <c r="P6" s="10"/>
-    </row>
-    <row r="7" spans="1:16" s="29" customFormat="1" ht="87" customHeight="1">
-      <c r="A7" s="9" t="s">
+      <c r="I6" s="40"/>
+      <c r="J6" s="40"/>
+      <c r="K6" s="45"/>
+      <c r="L6" s="40"/>
+      <c r="M6" s="40"/>
+      <c r="N6" s="40"/>
+      <c r="O6" s="40"/>
+      <c r="P6" s="40"/>
+      <c r="Q6" s="40"/>
+    </row>
+    <row r="7" spans="1:17" s="23" customFormat="1" ht="87" customHeight="1">
+      <c r="A7" s="40" t="s">
         <v>81</v>
       </c>
-      <c r="B7" s="27" t="s">
+      <c r="B7" s="45" t="s">
         <v>54</v>
       </c>
-      <c r="C7" s="27" t="s">
+      <c r="C7" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="27" t="s">
+      <c r="D7" s="45" t="s">
         <v>53</v>
       </c>
-      <c r="E7" s="9"/>
-      <c r="F7" s="9"/>
-      <c r="G7" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="H7" s="32" t="s">
+      <c r="E7" s="40"/>
+      <c r="F7" s="40"/>
+      <c r="G7" s="41" t="s">
+        <v>4</v>
+      </c>
+      <c r="H7" s="43" t="s">
         <v>113</v>
       </c>
-      <c r="I7" s="9"/>
-      <c r="J7" s="27"/>
-      <c r="K7" s="9"/>
-      <c r="L7" s="9"/>
-      <c r="M7" s="33"/>
-      <c r="N7" s="9"/>
-      <c r="O7" s="9"/>
-      <c r="P7" s="9"/>
-    </row>
-    <row r="8" spans="1:16" s="29" customFormat="1" ht="87" customHeight="1">
-      <c r="A8" s="9" t="s">
+      <c r="I7" s="43"/>
+      <c r="J7" s="40"/>
+      <c r="K7" s="45"/>
+      <c r="L7" s="40"/>
+      <c r="M7" s="40"/>
+      <c r="N7" s="46"/>
+      <c r="O7" s="40"/>
+      <c r="P7" s="40"/>
+      <c r="Q7" s="40"/>
+    </row>
+    <row r="8" spans="1:17" s="23" customFormat="1" ht="87" customHeight="1">
+      <c r="A8" s="40" t="s">
         <v>84</v>
       </c>
-      <c r="B8" s="27" t="s">
+      <c r="B8" s="45" t="s">
         <v>52</v>
       </c>
-      <c r="C8" s="27" t="s">
+      <c r="C8" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="47" t="s">
         <v>82</v>
       </c>
-      <c r="E8" s="9"/>
-      <c r="F8" s="9" t="s">
+      <c r="E8" s="40"/>
+      <c r="F8" s="40" t="s">
         <v>83</v>
       </c>
-      <c r="G8" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="H8" s="30" t="s">
+      <c r="G8" s="41" t="s">
+        <v>4</v>
+      </c>
+      <c r="H8" s="43" t="s">
         <v>114</v>
       </c>
-      <c r="I8" s="9"/>
-      <c r="J8" s="27"/>
-      <c r="K8" s="9"/>
-      <c r="L8" s="9"/>
-      <c r="M8" s="9"/>
-      <c r="N8" s="9"/>
-      <c r="O8" s="9"/>
-      <c r="P8" s="9"/>
-    </row>
-    <row r="9" spans="1:16" s="29" customFormat="1" ht="87" customHeight="1">
-      <c r="A9" s="9" t="s">
+      <c r="I8" s="43"/>
+      <c r="J8" s="40"/>
+      <c r="K8" s="45"/>
+      <c r="L8" s="40"/>
+      <c r="M8" s="40"/>
+      <c r="N8" s="40"/>
+      <c r="O8" s="40"/>
+      <c r="P8" s="40"/>
+      <c r="Q8" s="40"/>
+    </row>
+    <row r="9" spans="1:17" s="23" customFormat="1" ht="87" customHeight="1">
+      <c r="A9" s="40" t="s">
         <v>85</v>
       </c>
-      <c r="B9" s="27" t="s">
+      <c r="B9" s="45" t="s">
         <v>51</v>
       </c>
-      <c r="C9" s="27" t="s">
+      <c r="C9" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="27" t="s">
+      <c r="D9" s="45" t="s">
         <v>50</v>
       </c>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="H9" s="34" t="s">
+      <c r="E9" s="40"/>
+      <c r="F9" s="40"/>
+      <c r="G9" s="41" t="s">
+        <v>4</v>
+      </c>
+      <c r="H9" s="40" t="s">
         <v>116</v>
       </c>
-      <c r="I9" s="9"/>
-      <c r="J9" s="27"/>
-      <c r="K9" s="9"/>
-      <c r="L9" s="9"/>
-      <c r="M9" s="9"/>
-      <c r="N9" s="9"/>
-      <c r="O9" s="9"/>
-      <c r="P9" s="9"/>
-    </row>
-    <row r="10" spans="1:16" s="29" customFormat="1" ht="87" customHeight="1">
-      <c r="A10" s="9" t="s">
+      <c r="I9" s="40"/>
+      <c r="J9" s="40"/>
+      <c r="K9" s="45"/>
+      <c r="L9" s="40"/>
+      <c r="M9" s="40"/>
+      <c r="N9" s="40"/>
+      <c r="O9" s="40"/>
+      <c r="P9" s="40"/>
+      <c r="Q9" s="40"/>
+    </row>
+    <row r="10" spans="1:17" s="23" customFormat="1" ht="87" customHeight="1">
+      <c r="A10" s="40" t="s">
         <v>86</v>
       </c>
-      <c r="B10" s="27" t="s">
+      <c r="B10" s="45" t="s">
         <v>49</v>
       </c>
-      <c r="C10" s="27" t="s">
+      <c r="C10" s="45" t="s">
         <v>33</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="47" t="s">
         <v>90</v>
       </c>
-      <c r="E10" s="9"/>
-      <c r="F10" s="9" t="s">
+      <c r="E10" s="40"/>
+      <c r="F10" s="40" t="s">
         <v>91</v>
       </c>
-      <c r="G10" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="H10" s="32" t="s">
+      <c r="G10" s="41" t="s">
+        <v>4</v>
+      </c>
+      <c r="H10" s="43" t="s">
         <v>117</v>
       </c>
-      <c r="I10" s="9"/>
-      <c r="J10" s="27"/>
-      <c r="K10" s="9"/>
-      <c r="L10" s="9"/>
-      <c r="M10" s="9"/>
-      <c r="N10" s="9"/>
-      <c r="O10" s="9"/>
-      <c r="P10" s="9"/>
-    </row>
-    <row r="11" spans="1:16" s="29" customFormat="1" ht="87" customHeight="1">
-      <c r="A11" s="9" t="s">
+      <c r="I10" s="43"/>
+      <c r="J10" s="40"/>
+      <c r="K10" s="45"/>
+      <c r="L10" s="40"/>
+      <c r="M10" s="40"/>
+      <c r="N10" s="40"/>
+      <c r="O10" s="40"/>
+      <c r="P10" s="40"/>
+      <c r="Q10" s="40"/>
+    </row>
+    <row r="11" spans="1:17" s="23" customFormat="1" ht="87" customHeight="1">
+      <c r="A11" s="40" t="s">
         <v>87</v>
       </c>
-      <c r="B11" s="27" t="s">
+      <c r="B11" s="45" t="s">
         <v>48</v>
       </c>
-      <c r="C11" s="27" t="s">
+      <c r="C11" s="45" t="s">
         <v>33</v>
       </c>
-      <c r="D11" s="27" t="s">
+      <c r="D11" s="45" t="s">
         <v>47</v>
       </c>
-      <c r="E11" s="9"/>
-      <c r="F11" s="9"/>
-      <c r="G11" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="H11" s="32" t="s">
+      <c r="E11" s="40"/>
+      <c r="F11" s="40"/>
+      <c r="G11" s="41" t="s">
+        <v>4</v>
+      </c>
+      <c r="H11" s="43" t="s">
         <v>117</v>
       </c>
-      <c r="I11" s="9"/>
-      <c r="J11" s="27"/>
-      <c r="K11" s="9"/>
-      <c r="L11" s="9"/>
-      <c r="M11" s="9"/>
-      <c r="N11" s="9"/>
-      <c r="O11" s="9"/>
-      <c r="P11" s="9"/>
-    </row>
-    <row r="12" spans="1:16" s="29" customFormat="1" ht="87" customHeight="1">
-      <c r="A12" s="9" t="s">
+      <c r="I11" s="43"/>
+      <c r="J11" s="40"/>
+      <c r="K11" s="45"/>
+      <c r="L11" s="40"/>
+      <c r="M11" s="40"/>
+      <c r="N11" s="40"/>
+      <c r="O11" s="40"/>
+      <c r="P11" s="40"/>
+      <c r="Q11" s="40"/>
+    </row>
+    <row r="12" spans="1:17" s="23" customFormat="1" ht="87" customHeight="1">
+      <c r="A12" s="40" t="s">
         <v>88</v>
       </c>
-      <c r="B12" s="27" t="s">
+      <c r="B12" s="45" t="s">
         <v>46</v>
       </c>
-      <c r="C12" s="27" t="s">
+      <c r="C12" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" s="47" t="s">
         <v>92</v>
       </c>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9" t="s">
+      <c r="E12" s="40"/>
+      <c r="F12" s="40" t="s">
         <v>93</v>
       </c>
-      <c r="G12" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="H12" s="32" t="s">
+      <c r="G12" s="41" t="s">
+        <v>4</v>
+      </c>
+      <c r="H12" s="43" t="s">
         <v>118</v>
       </c>
-      <c r="I12" s="9"/>
-      <c r="J12" s="27"/>
-      <c r="K12" s="9"/>
-      <c r="L12" s="9"/>
-      <c r="M12" s="9"/>
-      <c r="N12" s="9"/>
-      <c r="O12" s="9"/>
-      <c r="P12" s="9"/>
-    </row>
-    <row r="13" spans="1:16" s="29" customFormat="1" ht="87" customHeight="1">
-      <c r="A13" s="9" t="s">
+      <c r="I12" s="43"/>
+      <c r="J12" s="40"/>
+      <c r="K12" s="45"/>
+      <c r="L12" s="40"/>
+      <c r="M12" s="40"/>
+      <c r="N12" s="40"/>
+      <c r="O12" s="40"/>
+      <c r="P12" s="40"/>
+      <c r="Q12" s="40"/>
+    </row>
+    <row r="13" spans="1:17" s="23" customFormat="1" ht="87" customHeight="1">
+      <c r="A13" s="40" t="s">
         <v>89</v>
       </c>
-      <c r="B13" s="27" t="s">
+      <c r="B13" s="45" t="s">
         <v>45</v>
       </c>
-      <c r="C13" s="27" t="s">
+      <c r="C13" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" s="47" t="s">
         <v>119</v>
       </c>
-      <c r="E13" s="9"/>
-      <c r="F13" s="9" t="s">
+      <c r="E13" s="40"/>
+      <c r="F13" s="40" t="s">
         <v>94</v>
       </c>
-      <c r="G13" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="H13" s="34" t="s">
+      <c r="G13" s="41" t="s">
+        <v>4</v>
+      </c>
+      <c r="H13" s="40" t="s">
         <v>120</v>
       </c>
-      <c r="I13" s="9"/>
-      <c r="J13" s="27"/>
-      <c r="K13" s="9"/>
-      <c r="L13" s="9"/>
-      <c r="M13" s="9"/>
-      <c r="N13" s="9"/>
-      <c r="O13" s="9"/>
-      <c r="P13" s="9"/>
-    </row>
-    <row r="14" spans="1:16" s="29" customFormat="1" ht="87" customHeight="1">
-      <c r="A14" s="9" t="s">
+      <c r="I13" s="40"/>
+      <c r="J13" s="40"/>
+      <c r="K13" s="45"/>
+      <c r="L13" s="40"/>
+      <c r="M13" s="40"/>
+      <c r="N13" s="40"/>
+      <c r="O13" s="40"/>
+      <c r="P13" s="40"/>
+      <c r="Q13" s="40"/>
+    </row>
+    <row r="14" spans="1:17" s="23" customFormat="1" ht="87" customHeight="1">
+      <c r="A14" s="40" t="s">
         <v>95</v>
       </c>
-      <c r="B14" s="27" t="s">
+      <c r="B14" s="45" t="s">
         <v>44</v>
       </c>
-      <c r="C14" s="27" t="s">
+      <c r="C14" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="D14" s="27" t="s">
+      <c r="D14" s="45" t="s">
         <v>43</v>
       </c>
-      <c r="E14" s="9"/>
-      <c r="F14" s="9"/>
-      <c r="G14" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="H14" s="32" t="s">
+      <c r="E14" s="40"/>
+      <c r="F14" s="40"/>
+      <c r="G14" s="41" t="s">
+        <v>4</v>
+      </c>
+      <c r="H14" s="43" t="s">
         <v>121</v>
       </c>
-      <c r="I14" s="9"/>
-      <c r="J14" s="27"/>
-      <c r="K14" s="9"/>
-      <c r="L14" s="9"/>
-      <c r="M14" s="9"/>
-      <c r="N14" s="9"/>
-      <c r="O14" s="9"/>
-      <c r="P14" s="9"/>
-    </row>
-    <row r="15" spans="1:16" s="29" customFormat="1" ht="87" customHeight="1">
-      <c r="A15" s="9" t="s">
+      <c r="I14" s="43"/>
+      <c r="J14" s="40"/>
+      <c r="K14" s="45"/>
+      <c r="L14" s="40"/>
+      <c r="M14" s="40"/>
+      <c r="N14" s="40"/>
+      <c r="O14" s="40"/>
+      <c r="P14" s="40"/>
+      <c r="Q14" s="40"/>
+    </row>
+    <row r="15" spans="1:17" s="23" customFormat="1" ht="87" customHeight="1">
+      <c r="A15" s="40" t="s">
         <v>96</v>
       </c>
-      <c r="B15" s="27" t="s">
+      <c r="B15" s="45" t="s">
         <v>42</v>
       </c>
-      <c r="C15" s="27" t="s">
+      <c r="C15" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="D15" s="27" t="s">
+      <c r="D15" s="45" t="s">
         <v>41</v>
       </c>
-      <c r="E15" s="9"/>
-      <c r="F15" s="25"/>
-      <c r="G15" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="H15" s="9" t="s">
+      <c r="E15" s="40"/>
+      <c r="F15" s="42"/>
+      <c r="G15" s="41" t="s">
+        <v>4</v>
+      </c>
+      <c r="H15" s="40" t="s">
         <v>122</v>
       </c>
-      <c r="I15" s="10"/>
-      <c r="J15" s="27"/>
-      <c r="K15" s="10"/>
-      <c r="L15" s="10"/>
-      <c r="M15" s="10"/>
-      <c r="N15" s="10"/>
-      <c r="O15" s="10"/>
-      <c r="P15" s="10"/>
-    </row>
-    <row r="16" spans="1:16" s="29" customFormat="1" ht="87" customHeight="1">
-      <c r="A16" s="9" t="s">
+      <c r="I15" s="40"/>
+      <c r="J15" s="40"/>
+      <c r="K15" s="45"/>
+      <c r="L15" s="40"/>
+      <c r="M15" s="40"/>
+      <c r="N15" s="40"/>
+      <c r="O15" s="40"/>
+      <c r="P15" s="40"/>
+      <c r="Q15" s="40"/>
+    </row>
+    <row r="16" spans="1:17" s="23" customFormat="1" ht="87" customHeight="1">
+      <c r="A16" s="40" t="s">
         <v>97</v>
       </c>
-      <c r="B16" s="27" t="s">
+      <c r="B16" s="45" t="s">
         <v>40</v>
       </c>
-      <c r="C16" s="27" t="s">
+      <c r="C16" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="D16" s="27" t="s">
+      <c r="D16" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="H16" s="35" t="s">
+      <c r="E16" s="40"/>
+      <c r="F16" s="40"/>
+      <c r="G16" s="41" t="s">
+        <v>4</v>
+      </c>
+      <c r="H16" s="43" t="s">
         <v>123</v>
       </c>
-      <c r="I16" s="9"/>
-      <c r="J16" s="27"/>
-      <c r="K16" s="9"/>
-      <c r="L16" s="9"/>
-      <c r="M16" s="9"/>
-      <c r="N16" s="9"/>
-      <c r="O16" s="9"/>
-      <c r="P16" s="9"/>
-    </row>
-    <row r="17" spans="1:16" s="29" customFormat="1" ht="87" customHeight="1">
-      <c r="A17" s="9" t="s">
+      <c r="I16" s="43"/>
+      <c r="J16" s="40"/>
+      <c r="K16" s="45"/>
+      <c r="L16" s="40"/>
+      <c r="M16" s="40"/>
+      <c r="N16" s="40"/>
+      <c r="O16" s="40"/>
+      <c r="P16" s="40"/>
+      <c r="Q16" s="40"/>
+    </row>
+    <row r="17" spans="1:17" s="23" customFormat="1" ht="87" customHeight="1">
+      <c r="A17" s="40" t="s">
         <v>98</v>
       </c>
-      <c r="B17" s="27" t="s">
+      <c r="B17" s="45" t="s">
         <v>38</v>
       </c>
-      <c r="C17" s="27" t="s">
+      <c r="C17" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="D17" s="27" t="s">
+      <c r="D17" s="45" t="s">
         <v>37</v>
       </c>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="H17" s="35" t="s">
+      <c r="E17" s="40"/>
+      <c r="F17" s="40"/>
+      <c r="G17" s="41" t="s">
+        <v>4</v>
+      </c>
+      <c r="H17" s="43" t="s">
         <v>123</v>
       </c>
-      <c r="I17" s="9"/>
-      <c r="J17" s="27"/>
-      <c r="K17" s="9"/>
-      <c r="L17" s="9"/>
-      <c r="M17" s="9"/>
-      <c r="N17" s="9"/>
-      <c r="O17" s="9"/>
-      <c r="P17" s="9"/>
-    </row>
-    <row r="18" spans="1:16" s="29" customFormat="1" ht="87" customHeight="1">
-      <c r="A18" s="9" t="s">
+      <c r="I17" s="43"/>
+      <c r="J17" s="40"/>
+      <c r="K17" s="45"/>
+      <c r="L17" s="40"/>
+      <c r="M17" s="40"/>
+      <c r="N17" s="40"/>
+      <c r="O17" s="40"/>
+      <c r="P17" s="40"/>
+      <c r="Q17" s="40"/>
+    </row>
+    <row r="18" spans="1:17" s="23" customFormat="1" ht="87" customHeight="1">
+      <c r="A18" s="40" t="s">
         <v>99</v>
       </c>
-      <c r="B18" s="27" t="s">
+      <c r="B18" s="45" t="s">
         <v>36</v>
       </c>
-      <c r="C18" s="27" t="s">
+      <c r="C18" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="D18" s="27" t="s">
+      <c r="D18" s="45" t="s">
         <v>35</v>
       </c>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="H18" s="35" t="s">
+      <c r="E18" s="40"/>
+      <c r="F18" s="40"/>
+      <c r="G18" s="41" t="s">
+        <v>4</v>
+      </c>
+      <c r="H18" s="43" t="s">
         <v>123</v>
       </c>
-      <c r="I18" s="9"/>
-      <c r="J18" s="27"/>
-      <c r="K18" s="9"/>
-      <c r="L18" s="9"/>
-      <c r="M18" s="9"/>
-      <c r="N18" s="9"/>
-      <c r="O18" s="9"/>
-      <c r="P18" s="9"/>
-    </row>
-    <row r="19" spans="1:16" s="29" customFormat="1" ht="87" customHeight="1">
-      <c r="A19" s="9" t="s">
+      <c r="I18" s="43"/>
+      <c r="J18" s="40"/>
+      <c r="K18" s="45"/>
+      <c r="L18" s="40"/>
+      <c r="M18" s="40"/>
+      <c r="N18" s="40"/>
+      <c r="O18" s="40"/>
+      <c r="P18" s="40"/>
+      <c r="Q18" s="40"/>
+    </row>
+    <row r="19" spans="1:17" s="23" customFormat="1" ht="87" customHeight="1">
+      <c r="A19" s="40" t="s">
         <v>100</v>
       </c>
-      <c r="B19" s="27" t="s">
+      <c r="B19" s="45" t="s">
         <v>34</v>
       </c>
-      <c r="C19" s="27" t="s">
+      <c r="C19" s="45" t="s">
         <v>33</v>
       </c>
-      <c r="D19" s="27" t="s">
+      <c r="D19" s="45" t="s">
         <v>32</v>
       </c>
-      <c r="E19" s="9"/>
-      <c r="F19" s="25"/>
-      <c r="G19" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="H19" s="35" t="s">
+      <c r="E19" s="40"/>
+      <c r="F19" s="42"/>
+      <c r="G19" s="41" t="s">
+        <v>4</v>
+      </c>
+      <c r="H19" s="43" t="s">
         <v>124</v>
       </c>
-      <c r="I19" s="9"/>
-      <c r="J19" s="27"/>
-      <c r="K19" s="9"/>
-      <c r="L19" s="9"/>
-      <c r="M19" s="9"/>
-      <c r="N19" s="9"/>
-      <c r="O19" s="9"/>
-      <c r="P19" s="9"/>
-    </row>
-    <row r="20" spans="1:16" s="29" customFormat="1" ht="87" customHeight="1">
-      <c r="A20" s="9" t="s">
+      <c r="I19" s="43"/>
+      <c r="J19" s="40"/>
+      <c r="K19" s="45"/>
+      <c r="L19" s="40"/>
+      <c r="M19" s="40"/>
+      <c r="N19" s="40"/>
+      <c r="O19" s="40"/>
+      <c r="P19" s="40"/>
+      <c r="Q19" s="40"/>
+    </row>
+    <row r="20" spans="1:17" s="23" customFormat="1" ht="87" customHeight="1">
+      <c r="A20" s="40" t="s">
         <v>101</v>
       </c>
-      <c r="B20" s="27" t="s">
+      <c r="B20" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="C20" s="27" t="s">
+      <c r="C20" s="45" t="s">
         <v>30</v>
       </c>
-      <c r="D20" s="27" t="s">
+      <c r="D20" s="45" t="s">
         <v>29</v>
       </c>
-      <c r="E20" s="9"/>
-      <c r="F20" s="25"/>
-      <c r="G20" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="H20" s="9" t="s">
+      <c r="E20" s="40"/>
+      <c r="F20" s="42"/>
+      <c r="G20" s="41" t="s">
+        <v>4</v>
+      </c>
+      <c r="H20" s="40" t="s">
         <v>125</v>
       </c>
-      <c r="I20" s="9"/>
-      <c r="J20" s="27"/>
-      <c r="K20" s="9"/>
-      <c r="L20" s="9"/>
-      <c r="M20" s="9"/>
-      <c r="N20" s="9"/>
-      <c r="O20" s="9"/>
-      <c r="P20" s="9"/>
-    </row>
-    <row r="21" spans="1:16" s="29" customFormat="1" ht="87" customHeight="1">
-      <c r="A21" s="9" t="s">
+      <c r="I20" s="40"/>
+      <c r="J20" s="40"/>
+      <c r="K20" s="45"/>
+      <c r="L20" s="40"/>
+      <c r="M20" s="40"/>
+      <c r="N20" s="40"/>
+      <c r="O20" s="40"/>
+      <c r="P20" s="40"/>
+      <c r="Q20" s="40"/>
+    </row>
+    <row r="21" spans="1:17" s="23" customFormat="1" ht="87" customHeight="1">
+      <c r="A21" s="40" t="s">
         <v>102</v>
       </c>
-      <c r="B21" s="27" t="s">
+      <c r="B21" s="45" t="s">
         <v>28</v>
       </c>
-      <c r="C21" s="27" t="s">
+      <c r="C21" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="D21" s="27" t="s">
+      <c r="D21" s="45" t="s">
         <v>27</v>
       </c>
-      <c r="E21" s="9"/>
-      <c r="F21" s="9"/>
-      <c r="G21" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="H21" s="9"/>
-      <c r="I21" s="9"/>
-      <c r="J21" s="27"/>
-      <c r="K21" s="9"/>
-      <c r="L21" s="9"/>
-      <c r="M21" s="9"/>
-      <c r="N21" s="9"/>
-      <c r="O21" s="9"/>
-      <c r="P21" s="9"/>
-    </row>
-    <row r="22" spans="1:16" s="29" customFormat="1" ht="87" customHeight="1">
-      <c r="A22" s="9" t="s">
+      <c r="E21" s="40"/>
+      <c r="F21" s="40"/>
+      <c r="G21" s="41" t="s">
+        <v>4</v>
+      </c>
+      <c r="H21" s="40"/>
+      <c r="I21" s="40"/>
+      <c r="J21" s="40"/>
+      <c r="K21" s="45"/>
+      <c r="L21" s="40"/>
+      <c r="M21" s="40"/>
+      <c r="N21" s="40"/>
+      <c r="O21" s="40"/>
+      <c r="P21" s="40"/>
+      <c r="Q21" s="40"/>
+    </row>
+    <row r="22" spans="1:17" s="23" customFormat="1" ht="87" customHeight="1">
+      <c r="A22" s="40" t="s">
         <v>103</v>
       </c>
-      <c r="B22" s="27" t="s">
+      <c r="B22" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="C22" s="27" t="s">
+      <c r="C22" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="D22" s="27" t="s">
+      <c r="D22" s="45" t="s">
         <v>25</v>
       </c>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9"/>
-      <c r="G22" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="H22" s="9"/>
-      <c r="I22" s="9"/>
-      <c r="J22" s="27"/>
-      <c r="K22" s="9"/>
-      <c r="L22" s="9"/>
-      <c r="M22" s="9"/>
-      <c r="N22" s="9"/>
-      <c r="O22" s="9"/>
-      <c r="P22" s="9"/>
-    </row>
-    <row r="23" spans="1:16" s="29" customFormat="1" ht="87" customHeight="1">
-      <c r="A23" s="9" t="s">
+      <c r="E22" s="40"/>
+      <c r="F22" s="40"/>
+      <c r="G22" s="41" t="s">
+        <v>4</v>
+      </c>
+      <c r="H22" s="40"/>
+      <c r="I22" s="40"/>
+      <c r="J22" s="40"/>
+      <c r="K22" s="45"/>
+      <c r="L22" s="40"/>
+      <c r="M22" s="40"/>
+      <c r="N22" s="40"/>
+      <c r="O22" s="40"/>
+      <c r="P22" s="40"/>
+      <c r="Q22" s="40"/>
+    </row>
+    <row r="23" spans="1:17" s="23" customFormat="1" ht="87" customHeight="1">
+      <c r="A23" s="40" t="s">
         <v>106</v>
       </c>
-      <c r="B23" s="27" t="s">
+      <c r="B23" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="C23" s="27" t="s">
+      <c r="C23" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="D23" s="27" t="s">
+      <c r="D23" s="45" t="s">
         <v>23</v>
       </c>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="H23" s="9"/>
-      <c r="I23" s="9"/>
-      <c r="J23" s="27"/>
-      <c r="K23" s="9"/>
-      <c r="L23" s="9"/>
-      <c r="M23" s="9"/>
-      <c r="N23" s="9"/>
-      <c r="O23" s="9"/>
-      <c r="P23" s="9"/>
-    </row>
-    <row r="24" spans="1:16" s="29" customFormat="1" ht="87" customHeight="1">
-      <c r="A24" s="9" t="s">
+      <c r="E23" s="40"/>
+      <c r="F23" s="40"/>
+      <c r="G23" s="41" t="s">
+        <v>4</v>
+      </c>
+      <c r="H23" s="40"/>
+      <c r="I23" s="40"/>
+      <c r="J23" s="40"/>
+      <c r="K23" s="45"/>
+      <c r="L23" s="40"/>
+      <c r="M23" s="40"/>
+      <c r="N23" s="40"/>
+      <c r="O23" s="40"/>
+      <c r="P23" s="40"/>
+      <c r="Q23" s="40"/>
+    </row>
+    <row r="24" spans="1:17" s="23" customFormat="1" ht="87" customHeight="1">
+      <c r="A24" s="40" t="s">
         <v>104</v>
       </c>
-      <c r="B24" s="27" t="s">
+      <c r="B24" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="C24" s="27" t="s">
+      <c r="C24" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="27" t="s">
+      <c r="D24" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="E24" s="9"/>
-      <c r="F24" s="9"/>
-      <c r="G24" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="H24" s="9"/>
-      <c r="I24" s="9"/>
-      <c r="J24" s="27"/>
-      <c r="K24" s="9"/>
-      <c r="L24" s="9"/>
-      <c r="M24" s="9"/>
-      <c r="N24" s="9"/>
-      <c r="O24" s="9"/>
-      <c r="P24" s="9"/>
-    </row>
-    <row r="25" spans="1:16" s="29" customFormat="1" ht="87" customHeight="1">
-      <c r="A25" s="9" t="s">
+      <c r="E24" s="40"/>
+      <c r="F24" s="40"/>
+      <c r="G24" s="41" t="s">
+        <v>4</v>
+      </c>
+      <c r="H24" s="40"/>
+      <c r="I24" s="40"/>
+      <c r="J24" s="40"/>
+      <c r="K24" s="45"/>
+      <c r="L24" s="40"/>
+      <c r="M24" s="40"/>
+      <c r="N24" s="40"/>
+      <c r="O24" s="40"/>
+      <c r="P24" s="40"/>
+      <c r="Q24" s="40"/>
+    </row>
+    <row r="25" spans="1:17" s="23" customFormat="1" ht="87" customHeight="1">
+      <c r="A25" s="40" t="s">
         <v>105</v>
       </c>
-      <c r="B25" s="27" t="s">
+      <c r="B25" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="C25" s="27" t="s">
+      <c r="C25" s="45" t="s">
         <v>19</v>
       </c>
-      <c r="D25" s="27" t="s">
+      <c r="D25" s="45" t="s">
         <v>18</v>
       </c>
-      <c r="E25" s="36"/>
-      <c r="F25" s="36"/>
-      <c r="G25" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="H25" s="36"/>
-      <c r="I25" s="36"/>
-      <c r="J25" s="27"/>
-      <c r="K25" s="36"/>
-      <c r="L25" s="36"/>
-      <c r="M25" s="36"/>
-      <c r="N25" s="36"/>
-      <c r="O25" s="36"/>
-      <c r="P25" s="36"/>
-    </row>
-    <row r="26" spans="1:16" s="29" customFormat="1" ht="87" customHeight="1">
-      <c r="A26" s="9" t="s">
+      <c r="E25" s="48"/>
+      <c r="F25" s="48"/>
+      <c r="G25" s="41" t="s">
+        <v>4</v>
+      </c>
+      <c r="H25" s="48"/>
+      <c r="I25" s="48"/>
+      <c r="J25" s="48"/>
+      <c r="K25" s="45"/>
+      <c r="L25" s="48"/>
+      <c r="M25" s="48"/>
+      <c r="N25" s="48"/>
+      <c r="O25" s="48"/>
+      <c r="P25" s="48"/>
+      <c r="Q25" s="48"/>
+    </row>
+    <row r="26" spans="1:17" s="23" customFormat="1" ht="87" customHeight="1">
+      <c r="A26" s="40" t="s">
         <v>107</v>
       </c>
-      <c r="B26" s="27" t="s">
+      <c r="B26" s="45" t="s">
         <v>17</v>
       </c>
-      <c r="C26" s="27" t="s">
+      <c r="C26" s="45" t="s">
         <v>16</v>
       </c>
-      <c r="D26" s="27" t="s">
+      <c r="D26" s="45" t="s">
         <v>108</v>
       </c>
-      <c r="E26" s="36"/>
-      <c r="F26" s="36" t="s">
+      <c r="E26" s="48"/>
+      <c r="F26" s="48" t="s">
         <v>109</v>
       </c>
-      <c r="G26" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="H26" s="36" t="s">
+      <c r="G26" s="41" t="s">
+        <v>4</v>
+      </c>
+      <c r="H26" s="48" t="s">
         <v>126</v>
       </c>
-      <c r="I26" s="36"/>
-      <c r="J26" s="27"/>
-      <c r="K26" s="36"/>
-      <c r="L26" s="36"/>
-      <c r="M26" s="36"/>
-      <c r="N26" s="36"/>
-      <c r="O26" s="36"/>
-      <c r="P26" s="36"/>
-    </row>
-    <row r="27" spans="1:16" s="29" customFormat="1" ht="87" customHeight="1">
-      <c r="A27" s="9" t="s">
+      <c r="I26" s="48"/>
+      <c r="J26" s="48"/>
+      <c r="K26" s="45"/>
+      <c r="L26" s="48"/>
+      <c r="M26" s="48"/>
+      <c r="N26" s="48"/>
+      <c r="O26" s="48"/>
+      <c r="P26" s="48"/>
+      <c r="Q26" s="48"/>
+    </row>
+    <row r="27" spans="1:17" s="23" customFormat="1" ht="87" customHeight="1">
+      <c r="A27" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="B27" s="27" t="s">
+      <c r="B27" s="45" t="s">
         <v>14</v>
       </c>
-      <c r="C27" s="27" t="s">
+      <c r="C27" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="D27" s="27" t="s">
+      <c r="D27" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="E27" s="36"/>
-      <c r="F27" s="36"/>
-      <c r="G27" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="H27" s="36" t="s">
+      <c r="E27" s="48"/>
+      <c r="F27" s="48"/>
+      <c r="G27" s="41" t="s">
+        <v>4</v>
+      </c>
+      <c r="H27" s="48" t="s">
         <v>127</v>
       </c>
-      <c r="I27" s="27"/>
-      <c r="J27" s="27"/>
-      <c r="K27" s="36"/>
-      <c r="L27" s="36"/>
-      <c r="M27" s="36"/>
-      <c r="N27" s="36"/>
-      <c r="O27" s="36"/>
-      <c r="P27" s="27"/>
-    </row>
-    <row r="28" spans="1:16" s="29" customFormat="1" ht="87" customHeight="1">
-      <c r="A28" s="9" t="s">
+      <c r="I27" s="48"/>
+      <c r="J27" s="45"/>
+      <c r="K27" s="45"/>
+      <c r="L27" s="48"/>
+      <c r="M27" s="48"/>
+      <c r="N27" s="48"/>
+      <c r="O27" s="48"/>
+      <c r="P27" s="48"/>
+      <c r="Q27" s="45"/>
+    </row>
+    <row r="28" spans="1:17" s="23" customFormat="1" ht="87" customHeight="1">
+      <c r="A28" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="B28" s="27" t="s">
+      <c r="B28" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="C28" s="27" t="s">
+      <c r="C28" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="D28" s="27" t="s">
+      <c r="D28" s="45" t="s">
         <v>11</v>
       </c>
-      <c r="E28" s="27"/>
-      <c r="F28" s="27"/>
-      <c r="G28" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="H28" s="36" t="s">
+      <c r="E28" s="45"/>
+      <c r="F28" s="45"/>
+      <c r="G28" s="41" t="s">
+        <v>4</v>
+      </c>
+      <c r="H28" s="48" t="s">
         <v>127</v>
       </c>
-      <c r="I28" s="27"/>
-      <c r="J28" s="27"/>
-      <c r="K28" s="27"/>
-      <c r="L28" s="27"/>
-      <c r="M28" s="27"/>
-      <c r="N28" s="27"/>
-      <c r="O28" s="27"/>
-      <c r="P28" s="27"/>
-    </row>
-    <row r="29" spans="1:16" s="29" customFormat="1" ht="87" customHeight="1">
-      <c r="A29" s="9" t="s">
+      <c r="I28" s="48"/>
+      <c r="J28" s="45"/>
+      <c r="K28" s="45"/>
+      <c r="L28" s="45"/>
+      <c r="M28" s="45"/>
+      <c r="N28" s="45"/>
+      <c r="O28" s="45"/>
+      <c r="P28" s="45"/>
+      <c r="Q28" s="45"/>
+    </row>
+    <row r="29" spans="1:17" s="23" customFormat="1" ht="87" customHeight="1">
+      <c r="A29" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="B29" s="27" t="s">
+      <c r="B29" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="C29" s="27" t="s">
+      <c r="C29" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="D29" s="27" t="s">
+      <c r="D29" s="45" t="s">
         <v>9</v>
       </c>
-      <c r="E29" s="27"/>
-      <c r="F29" s="27"/>
-      <c r="G29" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="H29" s="36" t="s">
+      <c r="E29" s="45"/>
+      <c r="F29" s="45"/>
+      <c r="G29" s="41" t="s">
+        <v>4</v>
+      </c>
+      <c r="H29" s="48" t="s">
         <v>127</v>
       </c>
-      <c r="I29" s="27"/>
-      <c r="J29" s="27"/>
-      <c r="K29" s="27"/>
-      <c r="L29" s="27"/>
-      <c r="M29" s="27"/>
-      <c r="N29" s="27"/>
-      <c r="O29" s="27"/>
-      <c r="P29" s="27"/>
-    </row>
-    <row r="30" spans="1:16" s="29" customFormat="1" ht="87" customHeight="1">
-      <c r="A30" s="9" t="s">
+      <c r="I29" s="48"/>
+      <c r="J29" s="45"/>
+      <c r="K29" s="45"/>
+      <c r="L29" s="45"/>
+      <c r="M29" s="45"/>
+      <c r="N29" s="45"/>
+      <c r="O29" s="45"/>
+      <c r="P29" s="45"/>
+      <c r="Q29" s="45"/>
+    </row>
+    <row r="30" spans="1:17" s="23" customFormat="1" ht="87" customHeight="1">
+      <c r="A30" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="B30" s="27" t="s">
+      <c r="B30" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="C30" s="27" t="s">
+      <c r="C30" s="45" t="s">
         <v>7</v>
       </c>
-      <c r="D30" s="27" t="s">
+      <c r="D30" s="45" t="s">
         <v>6</v>
       </c>
-      <c r="E30" s="27"/>
-      <c r="F30" s="27"/>
-      <c r="G30" s="28" t="s">
-        <v>4</v>
-      </c>
-      <c r="H30" s="36" t="s">
+      <c r="E30" s="45"/>
+      <c r="F30" s="45"/>
+      <c r="G30" s="41" t="s">
+        <v>4</v>
+      </c>
+      <c r="H30" s="48" t="s">
         <v>127</v>
       </c>
-      <c r="I30" s="27"/>
-      <c r="J30" s="27"/>
-      <c r="K30" s="27"/>
-      <c r="L30" s="27"/>
-      <c r="M30" s="27"/>
-      <c r="N30" s="27"/>
-      <c r="O30" s="27"/>
-      <c r="P30" s="27"/>
-    </row>
-    <row r="31" spans="1:16" s="29" customFormat="1" ht="87" customHeight="1"/>
+      <c r="I30" s="48"/>
+      <c r="J30" s="45"/>
+      <c r="K30" s="45"/>
+      <c r="L30" s="45"/>
+      <c r="M30" s="45"/>
+      <c r="N30" s="45"/>
+      <c r="O30" s="45"/>
+      <c r="P30" s="45"/>
+      <c r="Q30" s="45"/>
+    </row>
+    <row r="31" spans="1:17" s="23" customFormat="1" ht="87" customHeight="1"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="B1:G1"/>
-    <mergeCell ref="J1:O1"/>
-    <mergeCell ref="H1:I1"/>
+    <mergeCell ref="K1:P1"/>
+    <mergeCell ref="H1:J1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="4294967293" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD5FE330-E567-4C63-B9B4-AD0BE082165A}">
   <dimension ref="A1:C29"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="250" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:3" ht="15">
+      <c r="A1" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="28">
+    <row r="2" spans="1:3" ht="28.5">
       <c r="A2" t="s">
         <v>61</v>
       </c>
       <c r="B2" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>64</v>
       </c>
     </row>
@@ -3124,14 +3236,14 @@
         <v>53</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="56">
+    <row r="7" spans="1:3" ht="57">
       <c r="A7" t="s">
         <v>52</v>
       </c>
       <c r="B7" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>65</v>
       </c>
     </row>
@@ -3146,14 +3258,14 @@
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="42">
+    <row r="9" spans="1:3" ht="42.75">
       <c r="A9" t="s">
         <v>49</v>
       </c>
       <c r="B9" t="s">
         <v>33</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="4" t="s">
         <v>66</v>
       </c>
     </row>
@@ -3168,25 +3280,25 @@
         <v>47</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="28">
+    <row r="11" spans="1:3" ht="28.5">
       <c r="A11" t="s">
         <v>46</v>
       </c>
       <c r="B11" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="4" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="42">
+    <row r="12" spans="1:3" ht="42.75">
       <c r="A12" t="s">
         <v>45</v>
       </c>
       <c r="B12" t="s">
         <v>16</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="4" t="s">
         <v>68</v>
       </c>
     </row>
@@ -3595,16 +3707,16 @@
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C0237B64-00E3-41F7-846C-65A87C6720AA}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="4d568f87-b25f-475a-a26b-5a1bcde8677b"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="a486f84b-88b9-4459-bbe1-3ce207c7425f"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="a486f84b-88b9-4459-bbe1-3ce207c7425f"/>
-    <ds:schemaRef ds:uri="4d568f87-b25f-475a-a26b-5a1bcde8677b"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/ressources/tableaux-de-travail/GT_Dessertes_Tab_PointsEau.xlsx
+++ b/ressources/tableaux-de-travail/GT_Dessertes_Tab_PointsEau.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WS\zz_telechargement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F1BCF877-EF07-4148-8B00-E307556AB81E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88D946C0-50C2-4EE6-ABB1-ACAE5069B26B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-140" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-45" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="table_v1" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="140">
   <si>
     <t>Statut de l'élément pour la v2 du standard Dessertes</t>
   </si>
@@ -474,6 +474,21 @@
   </si>
   <si>
     <t>ok</t>
+  </si>
+  <si>
+    <t>HBE</t>
+  </si>
+  <si>
+    <t>perenne/non perenne</t>
+  </si>
+  <si>
+    <t>classification sur l'intérêt opérationnel</t>
+  </si>
+  <si>
+    <t>autres ressources en eau = eau potable de reserve/ressources naturelles</t>
+  </si>
+  <si>
+    <t>autre attribut?</t>
   </si>
 </sst>
 </file>
@@ -680,7 +695,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -822,6 +837,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2175,7 +2193,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D536427B-83A6-4707-8C45-6BB4F1975BE7}">
-  <dimension ref="A1:Q31"/>
+  <dimension ref="A1:Q35"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.625" defaultRowHeight="87" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="10" style="18" customWidth="1"/>
@@ -3149,7 +3167,111 @@
       <c r="P30" s="45"/>
       <c r="Q30" s="45"/>
     </row>
-    <row r="31" spans="1:17" s="23" customFormat="1" ht="87" customHeight="1"/>
+    <row r="31" spans="1:17" s="23" customFormat="1" ht="87" customHeight="1">
+      <c r="A31" s="21" t="s">
+        <v>135</v>
+      </c>
+      <c r="B31" s="21"/>
+      <c r="C31" s="21"/>
+      <c r="D31" s="21"/>
+      <c r="E31" s="21"/>
+      <c r="F31" s="21"/>
+      <c r="G31" s="21"/>
+      <c r="H31" s="21"/>
+      <c r="I31" s="21"/>
+      <c r="J31" s="21"/>
+      <c r="K31" s="21"/>
+      <c r="L31" s="21"/>
+      <c r="M31" s="21"/>
+      <c r="N31" s="21"/>
+      <c r="O31" s="21"/>
+      <c r="P31" s="21"/>
+      <c r="Q31" s="21"/>
+    </row>
+    <row r="32" spans="1:17" ht="87" customHeight="1">
+      <c r="A32" s="50" t="s">
+        <v>136</v>
+      </c>
+      <c r="B32" s="50"/>
+      <c r="C32" s="50"/>
+      <c r="D32" s="50"/>
+      <c r="E32" s="50"/>
+      <c r="F32" s="50"/>
+      <c r="G32" s="50"/>
+      <c r="H32" s="50"/>
+      <c r="I32" s="50"/>
+      <c r="J32" s="50"/>
+      <c r="K32" s="50"/>
+      <c r="L32" s="50"/>
+      <c r="M32" s="50"/>
+      <c r="N32" s="50"/>
+      <c r="O32" s="50"/>
+      <c r="P32" s="50"/>
+      <c r="Q32" s="50"/>
+    </row>
+    <row r="33" spans="1:17" ht="87" customHeight="1">
+      <c r="A33" s="50" t="s">
+        <v>138</v>
+      </c>
+      <c r="B33" s="50"/>
+      <c r="C33" s="50"/>
+      <c r="D33" s="50"/>
+      <c r="E33" s="50"/>
+      <c r="F33" s="50"/>
+      <c r="G33" s="50"/>
+      <c r="H33" s="50"/>
+      <c r="I33" s="50"/>
+      <c r="J33" s="50"/>
+      <c r="K33" s="50"/>
+      <c r="L33" s="50"/>
+      <c r="M33" s="50"/>
+      <c r="N33" s="50"/>
+      <c r="O33" s="50"/>
+      <c r="P33" s="50"/>
+      <c r="Q33" s="50"/>
+    </row>
+    <row r="34" spans="1:17" ht="87" customHeight="1">
+      <c r="A34" s="50" t="s">
+        <v>137</v>
+      </c>
+      <c r="B34" s="50"/>
+      <c r="C34" s="50"/>
+      <c r="D34" s="50"/>
+      <c r="E34" s="50"/>
+      <c r="F34" s="50"/>
+      <c r="G34" s="50"/>
+      <c r="H34" s="50"/>
+      <c r="I34" s="50"/>
+      <c r="J34" s="50"/>
+      <c r="K34" s="50"/>
+      <c r="L34" s="50"/>
+      <c r="M34" s="50"/>
+      <c r="N34" s="50"/>
+      <c r="O34" s="50"/>
+      <c r="P34" s="50"/>
+      <c r="Q34" s="50"/>
+    </row>
+    <row r="35" spans="1:17" ht="87" customHeight="1">
+      <c r="A35" s="50" t="s">
+        <v>139</v>
+      </c>
+      <c r="B35" s="50"/>
+      <c r="C35" s="50"/>
+      <c r="D35" s="50"/>
+      <c r="E35" s="50"/>
+      <c r="F35" s="50"/>
+      <c r="G35" s="50"/>
+      <c r="H35" s="50"/>
+      <c r="I35" s="50"/>
+      <c r="J35" s="50"/>
+      <c r="K35" s="50"/>
+      <c r="L35" s="50"/>
+      <c r="M35" s="50"/>
+      <c r="N35" s="50"/>
+      <c r="O35" s="50"/>
+      <c r="P35" s="50"/>
+      <c r="Q35" s="50"/>
+    </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="B1:G1"/>

--- a/ressources/tableaux-de-travail/GT_Dessertes_Tab_PointsEau.xlsx
+++ b/ressources/tableaux-de-travail/GT_Dessertes_Tab_PointsEau.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WS\zz_telechargement\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88D946C0-50C2-4EE6-ABB1-ACAE5069B26B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B9D383D-6FF5-4AEE-B904-6084921D0211}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-45" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,6 +18,7 @@
     <sheet name="Standard AFIGEO" sheetId="5" r:id="rId3"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">table_modif!$A$2:$R$36</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">table_v1!$A$2:$R$2</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="625" uniqueCount="197">
   <si>
     <t>Statut de l'élément pour la v2 du standard Dessertes</t>
   </si>
@@ -489,13 +490,227 @@
   </si>
   <si>
     <t>autre attribut?</t>
+  </si>
+  <si>
+    <t>S'il n'y a pas de servitude DFCI, il n'y a pas de gestionnaire.
+Conserver tel quel mais en Optionnel</t>
+  </si>
+  <si>
+    <t>Laisser vide, identifiant créé automatiquement lors de la première intégration à la BD TOPO</t>
+  </si>
+  <si>
+    <t>identifiant BD TOPO (à faire évoluer)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Changer de nom/description 
+Pas forcément que les SDIS qui crée cet identifiant. Ne pas le rendre contraignant dans sa production
+</t>
+  </si>
+  <si>
+    <t>Optionnel</t>
+  </si>
+  <si>
+    <t>num_PEI</t>
+  </si>
+  <si>
+    <t>Numéro Gestionnaire</t>
+  </si>
+  <si>
+    <t>Numéro interne du PEI pour le gestionnaire.</t>
+  </si>
+  <si>
+    <t>Numéro ou référence du PEI</t>
+  </si>
+  <si>
+    <t>Numéro de référence du PEI validé en interservices. Il fortement recommandé d'indiquer ici l'identifiant SDIS du PEI s'il existe.</t>
+  </si>
+  <si>
+    <t>Identifiant BD TOPO</t>
+  </si>
+  <si>
+    <t>- Points d’eau naturels ou artificiels
+- Points de puisage
+- Réseaux d’irrigation agricoles
+- Autres réseaux d’eau sous pression
+- Citernes enterrées, bâches à eau, citernes aériennes et autres
+réserves fixes
+- Autres dispositifs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- PI (Poteau d’Incendie), 
+- BI (Prise d’eau sous pression, notamment bouche d’incendie), 
+- PA (Point d’aspiration aménagé), 
+- CI (Citerne aérienne ou enterrée). </t>
+  </si>
+  <si>
+    <t>- PI (Poteau d’Incendie), 
+- BI (Prise d’eau sous pression, notamment bouche d’incendie), 
+- PA (Point d’aspiration aménagé), 
+- CI (Citerne aérienne ou enterrée)
+- Autre</t>
+  </si>
+  <si>
+    <t>Liste</t>
+  </si>
+  <si>
+    <t>Passer en Optionnel
+GT doit voir en interne à rendre la liste la plus complète possible. 
+Ecrire que si besoin de faire évoluer la liste, faire remonter côté IGN</t>
+  </si>
+  <si>
+    <t>Indiquer de remplir le champ type_rd si "Autre"
+retravailler les exigences de modélisation avec le GT : 
+si PI ou BI alors vide
+si PA alors ...
+si CI alors ...
+si Autre alors ..</t>
+  </si>
+  <si>
+    <t>sous_type_pei</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Précision sur le type de point d’eau incendie </t>
+  </si>
+  <si>
+    <t>Ne rentre pas dans le cadre de notre standard
+Attribut non conservé</t>
+  </si>
+  <si>
+    <t>supp</t>
+  </si>
+  <si>
+    <t>Redondant avec Précision sur le type de point d'eau</t>
+  </si>
+  <si>
+    <t>- Points d’eau naturels ou artificiels
+- Points de puisage
+- Réseaux d’irrigation agricoles
+- Autres réseaux d’eau sous pression
+- Citernes enterrées, bâches à eau, citernes aériennes et autres réserves fixes
+- plan_eau
+- piscine
+- puits 
+- cours_eau
+- Forage DFCI
+- forage agricole (mettre les deux si la distinction ne peut pas se faire plus loin)
+- Autres dispositifs</t>
+  </si>
+  <si>
+    <t>Donnée trop sensible pour être remontée au niveau national</t>
+  </si>
+  <si>
+    <t xml:space="preserve">information déjà harmonisée au niveau de la BD TOPO, cham à supprimé
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">information non pertinente 
+</t>
+  </si>
+  <si>
+    <t>Capacité volumique utile de la source d’eau en m3. Si la source est inépuisable, mettre 9999.</t>
+  </si>
+  <si>
+    <t>Dans la BD TOPO, on a aussi la date de creation de l'objet (du ponctuel dans la BD). Champ existe déjà dans la BD TOPO (récupère ce champ). Pas de besoin de remontée nationale de l'historique de l'objet terrain</t>
+  </si>
+  <si>
+    <t>Methode d'acquisition</t>
+  </si>
+  <si>
+    <t>Liste dans la BD TOPO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A voir lors de l'intégration. Element qui ne semble pas pertinent au regard des besoins métiers mais à voir selon les règles mises en place pour la BD TOPO (dans GT diffusion du standard)
+Pour l'IGN, besoin de la méthode et ils déduisent </t>
+  </si>
+  <si>
+    <t xml:space="preserve">calculé directement, pas besoin de l'indiquer dans le standard
+</t>
+  </si>
+  <si>
+    <t>Accessibilité HBE</t>
+  </si>
+  <si>
+    <t>Liste dans BD TOPO, récupérer tele champ</t>
+  </si>
+  <si>
+    <t>Information déjà présente dans "Precision type de PEI"</t>
+  </si>
+  <si>
+    <t>Pas de typologie nécessaire</t>
+  </si>
+  <si>
+    <t>Nom en francais</t>
+  </si>
+  <si>
+    <t>Nom</t>
+  </si>
+  <si>
+    <t>Code INSEE (BD TOPO)</t>
+  </si>
+  <si>
+    <t>BD TOPO</t>
+  </si>
+  <si>
+    <t>identifiant créé automatiquement lors de la première intégration à la BD TOPO (Laisser vide si l'objet n'a pas encore été remonté dans la BD TOPO)</t>
+  </si>
+  <si>
+    <t>alphanumérique</t>
+  </si>
+  <si>
+    <t>ref_gestion</t>
+  </si>
+  <si>
+    <t>Nom du gestionnaire du PEI (information anonymisée)</t>
+  </si>
+  <si>
+    <t>Type de point d’eau incendie. La typologie issue du règlement national DECI et est évolutive si le réglement change.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Statut du point d’eau. La définition du statut est décrite dans le règlement national de la DECI.
+</t>
+  </si>
+  <si>
+    <t>- public
+- privé</t>
+  </si>
+  <si>
+    <t>voir BD TOPO et reprendre 2 champs (maj et création de l'objet)</t>
+  </si>
+  <si>
+    <t>access_hbe</t>
+  </si>
+  <si>
+    <t>Défini l'accessibilité du point par un HBE</t>
+  </si>
+  <si>
+    <t>- Léger 
+- Lourd
+- Non accessible (selon le type, peut rendre ce champ remplissable ou pas)</t>
+  </si>
+  <si>
+    <t>Après discussion, l'élément représente un enjeu à venir pour la DFCI et nous avons décidé de l'intégrer en optionnel.</t>
+  </si>
+  <si>
+    <t>Persistance (voir BD TOPO)</t>
+  </si>
+  <si>
+    <t>Pas de besoin supplémentaires remontés par le GT durant la séance</t>
+  </si>
+  <si>
+    <t>Liste à retravailler par le GT</t>
+  </si>
+  <si>
+    <t>Raccord BD TOPO</t>
+  </si>
+  <si>
+    <t>Attester l'absence de besoin dans le standard</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -573,14 +788,8 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -629,8 +838,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -690,12 +911,49 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -799,6 +1057,9 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -808,37 +1069,154 @@
     <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="11" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2193,23 +2571,31 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D536427B-83A6-4707-8C45-6BB4F1975BE7}">
-  <dimension ref="A1:Q35"/>
+  <dimension ref="A1:R36"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.625" defaultRowHeight="87" customHeight="1"/>
   <cols>
-    <col min="1" max="3" width="10" style="18" customWidth="1"/>
-    <col min="4" max="4" width="62.375" style="18" customWidth="1"/>
-    <col min="5" max="5" width="10" style="18" customWidth="1"/>
-    <col min="6" max="6" width="21.125" style="18" customWidth="1"/>
-    <col min="7" max="7" width="10" style="18" customWidth="1"/>
-    <col min="8" max="8" width="59.375" style="18" customWidth="1"/>
-    <col min="9" max="9" width="36.875" style="18" customWidth="1"/>
+    <col min="1" max="1" width="10" style="18" customWidth="1"/>
+    <col min="2" max="2" width="17" style="18" customWidth="1"/>
+    <col min="3" max="3" width="9.375" style="18" customWidth="1"/>
+    <col min="4" max="4" width="38.75" style="18" customWidth="1"/>
+    <col min="5" max="5" width="5.75" style="18" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="30" style="18" customWidth="1"/>
+    <col min="7" max="7" width="17.375" style="18" customWidth="1"/>
+    <col min="8" max="8" width="17.75" style="51" customWidth="1"/>
+    <col min="9" max="9" width="11.625" style="18" customWidth="1"/>
     <col min="10" max="10" width="24.5" style="18" customWidth="1"/>
-    <col min="11" max="16" width="10" style="18" hidden="1" customWidth="1"/>
-    <col min="17" max="17" width="15.375" style="18" customWidth="1"/>
-    <col min="18" max="16384" width="10.625" style="18"/>
+    <col min="11" max="11" width="10" style="51" customWidth="1"/>
+    <col min="12" max="12" width="10" style="63" customWidth="1"/>
+    <col min="13" max="13" width="10" style="18" customWidth="1"/>
+    <col min="14" max="14" width="34.5" style="18" customWidth="1"/>
+    <col min="15" max="15" width="13" style="18" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="10" style="18" customWidth="1"/>
+    <col min="17" max="17" width="30.5" style="18" customWidth="1"/>
+    <col min="18" max="18" width="15.375" style="18" customWidth="1"/>
+    <col min="19" max="16384" width="10.625" style="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="87" customHeight="1">
+    <row r="1" spans="1:18" ht="87" customHeight="1">
       <c r="A1" s="10" t="s">
         <v>128</v>
       </c>
@@ -2220,25 +2606,26 @@
       <c r="D1" s="31"/>
       <c r="E1" s="31"/>
       <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="32" t="s">
+      <c r="G1" s="72"/>
+      <c r="H1" s="73" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="49"/>
-      <c r="J1" s="33"/>
-      <c r="K1" s="34" t="s">
+      <c r="I1" s="42"/>
+      <c r="J1" s="42"/>
+      <c r="K1" s="74" t="s">
         <v>129</v>
       </c>
       <c r="L1" s="35"/>
       <c r="M1" s="35"/>
       <c r="N1" s="35"/>
       <c r="O1" s="35"/>
-      <c r="P1" s="36"/>
-      <c r="Q1" s="11" t="s">
+      <c r="P1" s="35"/>
+      <c r="Q1" s="36"/>
+      <c r="R1" s="11" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="87" customHeight="1">
+    <row r="2" spans="1:18" ht="87" customHeight="1">
       <c r="A2" s="12" t="s">
         <v>2</v>
       </c>
@@ -2257,1025 +2644,1375 @@
       <c r="F2" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="52" t="s">
         <v>75</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="54" t="s">
         <v>130</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J2" s="45" t="s">
         <v>133</v>
       </c>
-      <c r="K2" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="L2" s="16" t="s">
+      <c r="K2" s="48" t="s">
+        <v>176</v>
+      </c>
+      <c r="L2" s="62" t="s">
+        <v>177</v>
+      </c>
+      <c r="M2" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="M2" s="16" t="s">
+      <c r="N2" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="N2" s="16" t="s">
+      <c r="O2" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="O2" s="16" t="s">
+      <c r="P2" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="P2" s="16" t="s">
+      <c r="Q2" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="Q2" s="13" t="s">
+      <c r="R2" s="13" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:17" s="23" customFormat="1" ht="60">
-      <c r="A3" s="37" t="s">
+    <row r="3" spans="1:18" s="23" customFormat="1" ht="105">
+      <c r="A3" s="84" t="s">
         <v>77</v>
       </c>
-      <c r="B3" s="44" t="s">
+      <c r="B3" s="77" t="s">
         <v>61</v>
       </c>
-      <c r="C3" s="44" t="s">
+      <c r="C3" s="77" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="38" t="s">
+      <c r="D3" s="76" t="s">
         <v>64</v>
       </c>
-      <c r="E3" s="37"/>
-      <c r="F3" s="37"/>
-      <c r="G3" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="H3" s="37" t="s">
+      <c r="E3" s="38"/>
+      <c r="F3" s="84"/>
+      <c r="G3" s="79" t="s">
+        <v>4</v>
+      </c>
+      <c r="H3" s="88" t="s">
         <v>110</v>
       </c>
-      <c r="I3" s="38" t="s">
+      <c r="I3" s="76" t="s">
         <v>134</v>
       </c>
-      <c r="J3" s="38"/>
-      <c r="K3" s="44"/>
-      <c r="L3" s="38"/>
-      <c r="M3" s="38"/>
-      <c r="N3" s="38"/>
-      <c r="O3" s="38"/>
-      <c r="P3" s="38"/>
-      <c r="Q3" s="38" t="s">
+      <c r="J3" s="81"/>
+      <c r="K3" s="85" t="s">
+        <v>178</v>
+      </c>
+      <c r="L3" s="65"/>
+      <c r="M3" s="66"/>
+      <c r="N3" s="66"/>
+      <c r="O3" s="66" t="s">
+        <v>179</v>
+      </c>
+      <c r="P3" s="66"/>
+      <c r="Q3" s="79" t="s">
+        <v>4</v>
+      </c>
+      <c r="R3" s="76" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" s="23" customFormat="1" ht="60">
+      <c r="A4" s="84"/>
+      <c r="B4" s="77" t="s">
+        <v>142</v>
+      </c>
+      <c r="C4" s="77"/>
+      <c r="D4" s="76"/>
+      <c r="E4" s="38"/>
+      <c r="F4" s="84"/>
+      <c r="G4" s="79"/>
+      <c r="H4" s="88"/>
+      <c r="I4" s="76"/>
+      <c r="J4" s="89" t="s">
+        <v>141</v>
+      </c>
+      <c r="K4" s="85" t="s">
+        <v>150</v>
+      </c>
+      <c r="L4" s="65"/>
+      <c r="M4" s="66"/>
+      <c r="N4" s="76" t="s">
+        <v>180</v>
+      </c>
+      <c r="O4" s="39" t="s">
+        <v>179</v>
+      </c>
+      <c r="P4" s="66"/>
+      <c r="Q4" s="84" t="s">
+        <v>144</v>
+      </c>
+      <c r="R4" s="76" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" s="23" customFormat="1" ht="87" customHeight="1">
+      <c r="A5" s="39" t="s">
+        <v>78</v>
+      </c>
+      <c r="B5" s="41" t="s">
+        <v>60</v>
+      </c>
+      <c r="C5" s="41" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="41" t="s">
+        <v>59</v>
+      </c>
+      <c r="E5" s="39"/>
+      <c r="F5" s="39"/>
+      <c r="G5" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="H5" s="55" t="s">
+        <v>115</v>
+      </c>
+      <c r="I5" s="40" t="s">
+        <v>132</v>
+      </c>
+      <c r="J5" s="44" t="s">
+        <v>143</v>
+      </c>
+      <c r="K5" s="50" t="s">
+        <v>148</v>
+      </c>
+      <c r="L5" s="41" t="s">
+        <v>145</v>
+      </c>
+      <c r="M5" s="41" t="s">
+        <v>181</v>
+      </c>
+      <c r="N5" s="41" t="s">
+        <v>149</v>
+      </c>
+      <c r="O5" s="43"/>
+      <c r="P5" s="39"/>
+      <c r="Q5" s="38" t="s">
+        <v>4</v>
+      </c>
+      <c r="R5" s="39" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="4" spans="1:17" s="23" customFormat="1" ht="87" customHeight="1">
-      <c r="A4" s="38" t="s">
-        <v>78</v>
-      </c>
-      <c r="B4" s="44" t="s">
-        <v>60</v>
-      </c>
-      <c r="C4" s="44" t="s">
+    <row r="6" spans="1:18" s="23" customFormat="1" ht="87" customHeight="1">
+      <c r="A6" s="39" t="s">
+        <v>79</v>
+      </c>
+      <c r="B6" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="C6" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="44" t="s">
-        <v>59</v>
-      </c>
-      <c r="E4" s="38"/>
-      <c r="F4" s="38"/>
-      <c r="G4" s="37" t="s">
-        <v>4</v>
-      </c>
-      <c r="H4" s="39" t="s">
-        <v>115</v>
-      </c>
-      <c r="I4" s="39" t="s">
-        <v>132</v>
-      </c>
-      <c r="J4" s="39"/>
-      <c r="K4" s="44"/>
-      <c r="L4" s="38"/>
-      <c r="M4" s="38"/>
-      <c r="N4" s="38"/>
-      <c r="O4" s="38"/>
-      <c r="P4" s="38"/>
-      <c r="Q4" s="38" t="s">
+      <c r="D6" s="41" t="s">
+        <v>57</v>
+      </c>
+      <c r="E6" s="39"/>
+      <c r="F6" s="39"/>
+      <c r="G6" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="H6" s="55" t="s">
+        <v>111</v>
+      </c>
+      <c r="I6" s="40"/>
+      <c r="J6" s="47" t="s">
+        <v>140</v>
+      </c>
+      <c r="K6" s="50" t="s">
+        <v>146</v>
+      </c>
+      <c r="L6" s="41" t="s">
+        <v>182</v>
+      </c>
+      <c r="M6" s="41" t="s">
+        <v>181</v>
+      </c>
+      <c r="N6" s="41" t="s">
+        <v>147</v>
+      </c>
+      <c r="O6" s="43"/>
+      <c r="P6" s="39"/>
+      <c r="Q6" s="38" t="s">
+        <v>144</v>
+      </c>
+      <c r="R6" s="39" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="5" spans="1:17" s="23" customFormat="1" ht="87" customHeight="1">
-      <c r="A5" s="40" t="s">
-        <v>79</v>
-      </c>
-      <c r="B5" s="45" t="s">
-        <v>58</v>
-      </c>
-      <c r="C5" s="45" t="s">
+    <row r="7" spans="1:18" s="43" customFormat="1" ht="87" customHeight="1">
+      <c r="A7" s="39" t="s">
+        <v>80</v>
+      </c>
+      <c r="B7" s="41" t="s">
+        <v>56</v>
+      </c>
+      <c r="C7" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="45" t="s">
-        <v>57</v>
-      </c>
-      <c r="E5" s="40"/>
-      <c r="F5" s="40"/>
-      <c r="G5" s="41" t="s">
-        <v>4</v>
-      </c>
-      <c r="H5" s="43" t="s">
-        <v>111</v>
-      </c>
-      <c r="I5" s="43"/>
-      <c r="J5" s="40"/>
-      <c r="K5" s="45"/>
-      <c r="L5" s="40"/>
-      <c r="M5" s="40"/>
-      <c r="N5" s="40"/>
-      <c r="O5" s="40"/>
-      <c r="P5" s="40"/>
-      <c r="Q5" s="40"/>
-    </row>
-    <row r="6" spans="1:17" s="23" customFormat="1" ht="87" customHeight="1">
-      <c r="A6" s="40" t="s">
+      <c r="D7" s="41" t="s">
+        <v>55</v>
+      </c>
+      <c r="E7" s="39"/>
+      <c r="F7" s="39"/>
+      <c r="G7" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="H7" s="50" t="s">
+        <v>112</v>
+      </c>
+      <c r="I7" s="39"/>
+      <c r="J7" s="46" t="s">
+        <v>134</v>
+      </c>
+      <c r="K7" s="50" t="s">
         <v>80</v>
       </c>
-      <c r="B6" s="45" t="s">
+      <c r="L7" s="41" t="s">
         <v>56</v>
       </c>
-      <c r="C6" s="45" t="s">
+      <c r="M7" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="45" t="s">
-        <v>55</v>
-      </c>
-      <c r="E6" s="40"/>
-      <c r="F6" s="40"/>
-      <c r="G6" s="41" t="s">
-        <v>4</v>
-      </c>
-      <c r="H6" s="40" t="s">
-        <v>112</v>
-      </c>
-      <c r="I6" s="40"/>
-      <c r="J6" s="40"/>
-      <c r="K6" s="45"/>
-      <c r="L6" s="40"/>
-      <c r="M6" s="40"/>
-      <c r="N6" s="40"/>
-      <c r="O6" s="40"/>
-      <c r="P6" s="40"/>
-      <c r="Q6" s="40"/>
-    </row>
-    <row r="7" spans="1:17" s="23" customFormat="1" ht="87" customHeight="1">
-      <c r="A7" s="40" t="s">
+      <c r="N7" s="41" t="s">
+        <v>183</v>
+      </c>
+      <c r="P7" s="39"/>
+      <c r="Q7" s="38" t="s">
+        <v>144</v>
+      </c>
+      <c r="R7" s="39" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" s="43" customFormat="1" ht="87" customHeight="1">
+      <c r="A8" s="39" t="s">
         <v>81</v>
       </c>
-      <c r="B7" s="45" t="s">
+      <c r="B8" s="41" t="s">
         <v>54</v>
       </c>
-      <c r="C7" s="45" t="s">
+      <c r="C8" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="45" t="s">
+      <c r="D8" s="41" t="s">
         <v>53</v>
       </c>
-      <c r="E7" s="40"/>
-      <c r="F7" s="40"/>
-      <c r="G7" s="41" t="s">
-        <v>4</v>
-      </c>
-      <c r="H7" s="43" t="s">
+      <c r="E8" s="39"/>
+      <c r="F8" s="39"/>
+      <c r="G8" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="H8" s="55" t="s">
         <v>113</v>
       </c>
-      <c r="I7" s="43"/>
-      <c r="J7" s="40"/>
-      <c r="K7" s="45"/>
-      <c r="L7" s="40"/>
-      <c r="M7" s="40"/>
-      <c r="N7" s="46"/>
-      <c r="O7" s="40"/>
-      <c r="P7" s="40"/>
-      <c r="Q7" s="40"/>
-    </row>
-    <row r="8" spans="1:17" s="23" customFormat="1" ht="87" customHeight="1">
-      <c r="A8" s="40" t="s">
+      <c r="I8" s="40"/>
+      <c r="J8" s="46"/>
+      <c r="K8" s="50" t="s">
+        <v>81</v>
+      </c>
+      <c r="L8" s="41" t="s">
+        <v>54</v>
+      </c>
+      <c r="M8" s="41" t="s">
+        <v>181</v>
+      </c>
+      <c r="N8" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="P8" s="39"/>
+      <c r="Q8" s="38" t="s">
+        <v>144</v>
+      </c>
+      <c r="R8" s="39" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" s="23" customFormat="1" ht="150" customHeight="1">
+      <c r="A9" s="76" t="s">
         <v>84</v>
       </c>
-      <c r="B8" s="45" t="s">
+      <c r="B9" s="77" t="s">
         <v>52</v>
       </c>
-      <c r="C8" s="45" t="s">
+      <c r="C9" s="77" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="47" t="s">
+      <c r="D9" s="76" t="s">
         <v>82</v>
       </c>
-      <c r="E8" s="40"/>
-      <c r="F8" s="40" t="s">
-        <v>83</v>
-      </c>
-      <c r="G8" s="41" t="s">
-        <v>4</v>
-      </c>
-      <c r="H8" s="43" t="s">
+      <c r="E9" s="76"/>
+      <c r="F9" s="78" t="s">
+        <v>152</v>
+      </c>
+      <c r="G9" s="79" t="s">
+        <v>4</v>
+      </c>
+      <c r="H9" s="80" t="s">
         <v>114</v>
       </c>
-      <c r="I8" s="43"/>
-      <c r="J8" s="40"/>
-      <c r="K8" s="45"/>
-      <c r="L8" s="40"/>
-      <c r="M8" s="40"/>
-      <c r="N8" s="40"/>
-      <c r="O8" s="40"/>
-      <c r="P8" s="40"/>
-      <c r="Q8" s="40"/>
-    </row>
-    <row r="9" spans="1:17" s="23" customFormat="1" ht="87" customHeight="1">
-      <c r="A9" s="40" t="s">
+      <c r="I9" s="78"/>
+      <c r="J9" s="81" t="s">
+        <v>156</v>
+      </c>
+      <c r="K9" s="82" t="s">
+        <v>84</v>
+      </c>
+      <c r="L9" s="77" t="s">
+        <v>52</v>
+      </c>
+      <c r="M9" s="77" t="s">
+        <v>154</v>
+      </c>
+      <c r="N9" s="76" t="s">
+        <v>184</v>
+      </c>
+      <c r="O9" s="83"/>
+      <c r="P9" s="75" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q9" s="84" t="s">
+        <v>4</v>
+      </c>
+      <c r="R9" s="76" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" s="23" customFormat="1" ht="274.5" customHeight="1">
+      <c r="A10" s="76" t="s">
         <v>85</v>
       </c>
-      <c r="B9" s="45" t="s">
+      <c r="B10" s="77" t="s">
         <v>51</v>
       </c>
-      <c r="C9" s="45" t="s">
+      <c r="C10" s="77" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="45" t="s">
+      <c r="D10" s="77" t="s">
         <v>50</v>
       </c>
-      <c r="E9" s="40"/>
-      <c r="F9" s="40"/>
-      <c r="G9" s="41" t="s">
-        <v>4</v>
-      </c>
-      <c r="H9" s="40" t="s">
+      <c r="E10" s="76"/>
+      <c r="F10" s="78" t="s">
+        <v>151</v>
+      </c>
+      <c r="G10" s="79" t="s">
+        <v>4</v>
+      </c>
+      <c r="H10" s="82" t="s">
         <v>116</v>
       </c>
-      <c r="I9" s="40"/>
-      <c r="J9" s="40"/>
-      <c r="K9" s="45"/>
-      <c r="L9" s="40"/>
-      <c r="M9" s="40"/>
-      <c r="N9" s="40"/>
-      <c r="O9" s="40"/>
-      <c r="P9" s="40"/>
-      <c r="Q9" s="40"/>
-    </row>
-    <row r="10" spans="1:17" s="23" customFormat="1" ht="87" customHeight="1">
-      <c r="A10" s="40" t="s">
+      <c r="I10" s="76"/>
+      <c r="J10" s="81" t="s">
+        <v>155</v>
+      </c>
+      <c r="K10" s="82" t="s">
+        <v>85</v>
+      </c>
+      <c r="L10" s="77" t="s">
+        <v>157</v>
+      </c>
+      <c r="M10" s="77" t="s">
+        <v>154</v>
+      </c>
+      <c r="N10" s="77" t="s">
+        <v>158</v>
+      </c>
+      <c r="O10" s="83"/>
+      <c r="P10" s="75" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q10" s="84" t="s">
+        <v>144</v>
+      </c>
+      <c r="R10" s="76" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" s="23" customFormat="1" ht="87" customHeight="1">
+      <c r="A11" s="39" t="s">
         <v>86</v>
       </c>
-      <c r="B10" s="45" t="s">
+      <c r="B11" s="41" t="s">
         <v>49</v>
       </c>
-      <c r="C10" s="45" t="s">
+      <c r="C11" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="D10" s="47" t="s">
+      <c r="D11" s="39" t="s">
         <v>90</v>
       </c>
-      <c r="E10" s="40"/>
-      <c r="F10" s="40" t="s">
+      <c r="E11" s="39"/>
+      <c r="F11" s="39" t="s">
         <v>91</v>
       </c>
-      <c r="G10" s="41" t="s">
-        <v>4</v>
-      </c>
-      <c r="H10" s="43" t="s">
+      <c r="G11" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="H11" s="55" t="s">
         <v>117</v>
       </c>
-      <c r="I10" s="43"/>
-      <c r="J10" s="40"/>
-      <c r="K10" s="45"/>
-      <c r="L10" s="40"/>
-      <c r="M10" s="40"/>
-      <c r="N10" s="40"/>
-      <c r="O10" s="40"/>
-      <c r="P10" s="40"/>
-      <c r="Q10" s="40"/>
-    </row>
-    <row r="11" spans="1:17" s="23" customFormat="1" ht="87" customHeight="1">
-      <c r="A11" s="40" t="s">
+      <c r="I11" s="40"/>
+      <c r="J11" s="46" t="s">
+        <v>159</v>
+      </c>
+      <c r="K11" s="49" t="s">
+        <v>160</v>
+      </c>
+      <c r="L11" s="39"/>
+      <c r="M11" s="39"/>
+      <c r="N11" s="39"/>
+      <c r="O11" s="43"/>
+      <c r="P11" s="39"/>
+      <c r="Q11" s="39"/>
+      <c r="R11" s="39" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" s="23" customFormat="1" ht="87" customHeight="1">
+      <c r="A12" s="39" t="s">
         <v>87</v>
       </c>
-      <c r="B11" s="45" t="s">
+      <c r="B12" s="41" t="s">
         <v>48</v>
       </c>
-      <c r="C11" s="45" t="s">
+      <c r="C12" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="D11" s="45" t="s">
+      <c r="D12" s="41" t="s">
         <v>47</v>
       </c>
-      <c r="E11" s="40"/>
-      <c r="F11" s="40"/>
-      <c r="G11" s="41" t="s">
-        <v>4</v>
-      </c>
-      <c r="H11" s="43" t="s">
+      <c r="E12" s="39"/>
+      <c r="F12" s="39"/>
+      <c r="G12" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="H12" s="55" t="s">
         <v>117</v>
       </c>
-      <c r="I11" s="43"/>
-      <c r="J11" s="40"/>
-      <c r="K11" s="45"/>
-      <c r="L11" s="40"/>
-      <c r="M11" s="40"/>
-      <c r="N11" s="40"/>
-      <c r="O11" s="40"/>
-      <c r="P11" s="40"/>
-      <c r="Q11" s="40"/>
-    </row>
-    <row r="12" spans="1:17" s="23" customFormat="1" ht="87" customHeight="1">
-      <c r="A12" s="40" t="s">
+      <c r="I12" s="40"/>
+      <c r="J12" s="46" t="s">
+        <v>159</v>
+      </c>
+      <c r="K12" s="49" t="s">
+        <v>160</v>
+      </c>
+      <c r="L12" s="39"/>
+      <c r="M12" s="39"/>
+      <c r="N12" s="39"/>
+      <c r="O12" s="43"/>
+      <c r="P12" s="39"/>
+      <c r="Q12" s="39"/>
+      <c r="R12" s="39" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" s="23" customFormat="1" ht="87" customHeight="1">
+      <c r="A13" s="39" t="s">
         <v>88</v>
       </c>
-      <c r="B12" s="45" t="s">
+      <c r="B13" s="41" t="s">
         <v>46</v>
       </c>
-      <c r="C12" s="45" t="s">
+      <c r="C13" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="D12" s="47" t="s">
+      <c r="D13" s="39" t="s">
         <v>92</v>
       </c>
-      <c r="E12" s="40"/>
-      <c r="F12" s="40" t="s">
+      <c r="E13" s="39"/>
+      <c r="F13" s="39" t="s">
         <v>93</v>
       </c>
-      <c r="G12" s="41" t="s">
-        <v>4</v>
-      </c>
-      <c r="H12" s="43" t="s">
+      <c r="G13" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="H13" s="55" t="s">
         <v>118</v>
       </c>
-      <c r="I12" s="43"/>
-      <c r="J12" s="40"/>
-      <c r="K12" s="45"/>
-      <c r="L12" s="40"/>
-      <c r="M12" s="40"/>
-      <c r="N12" s="40"/>
-      <c r="O12" s="40"/>
-      <c r="P12" s="40"/>
-      <c r="Q12" s="40"/>
-    </row>
-    <row r="13" spans="1:17" s="23" customFormat="1" ht="87" customHeight="1">
-      <c r="A13" s="40" t="s">
+      <c r="I13" s="40"/>
+      <c r="J13" s="46" t="s">
+        <v>161</v>
+      </c>
+      <c r="K13" s="50" t="s">
+        <v>160</v>
+      </c>
+      <c r="L13" s="41"/>
+      <c r="M13" s="41"/>
+      <c r="N13" s="39"/>
+      <c r="O13" s="43"/>
+      <c r="P13" s="39"/>
+      <c r="Q13" s="39"/>
+      <c r="R13" s="39" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" s="23" customFormat="1" ht="87" customHeight="1">
+      <c r="A14" s="39" t="s">
         <v>89</v>
       </c>
-      <c r="B13" s="45" t="s">
+      <c r="B14" s="41" t="s">
         <v>45</v>
       </c>
-      <c r="C13" s="45" t="s">
+      <c r="C14" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="D13" s="47" t="s">
+      <c r="D14" s="39" t="s">
         <v>119</v>
       </c>
-      <c r="E13" s="40"/>
-      <c r="F13" s="40" t="s">
+      <c r="E14" s="39"/>
+      <c r="F14" s="39" t="s">
         <v>94</v>
       </c>
-      <c r="G13" s="41" t="s">
-        <v>4</v>
-      </c>
-      <c r="H13" s="40" t="s">
+      <c r="G14" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="H14" s="50" t="s">
         <v>120</v>
       </c>
-      <c r="I13" s="40"/>
-      <c r="J13" s="40"/>
-      <c r="K13" s="45"/>
-      <c r="L13" s="40"/>
-      <c r="M13" s="40"/>
-      <c r="N13" s="40"/>
-      <c r="O13" s="40"/>
-      <c r="P13" s="40"/>
-      <c r="Q13" s="40"/>
-    </row>
-    <row r="14" spans="1:17" s="23" customFormat="1" ht="87" customHeight="1">
-      <c r="A14" s="40" t="s">
+      <c r="I14" s="39"/>
+      <c r="J14" s="46"/>
+      <c r="K14" s="50" t="s">
+        <v>89</v>
+      </c>
+      <c r="L14" s="41" t="s">
+        <v>45</v>
+      </c>
+      <c r="M14" s="41" t="s">
+        <v>154</v>
+      </c>
+      <c r="N14" s="39" t="s">
+        <v>185</v>
+      </c>
+      <c r="O14" s="43"/>
+      <c r="P14" s="40" t="s">
+        <v>186</v>
+      </c>
+      <c r="Q14" s="53" t="s">
+        <v>144</v>
+      </c>
+      <c r="R14" s="39" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" s="23" customFormat="1" ht="87" customHeight="1">
+      <c r="A15" s="39" t="s">
         <v>95</v>
       </c>
-      <c r="B14" s="45" t="s">
+      <c r="B15" s="41" t="s">
         <v>44</v>
       </c>
-      <c r="C14" s="45" t="s">
+      <c r="C15" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="D14" s="45" t="s">
+      <c r="D15" s="41" t="s">
         <v>43</v>
       </c>
-      <c r="E14" s="40"/>
-      <c r="F14" s="40"/>
-      <c r="G14" s="41" t="s">
-        <v>4</v>
-      </c>
-      <c r="H14" s="43" t="s">
+      <c r="E15" s="39"/>
+      <c r="F15" s="39"/>
+      <c r="G15" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="H15" s="55" t="s">
         <v>121</v>
       </c>
-      <c r="I14" s="43"/>
-      <c r="J14" s="40"/>
-      <c r="K14" s="45"/>
-      <c r="L14" s="40"/>
-      <c r="M14" s="40"/>
-      <c r="N14" s="40"/>
-      <c r="O14" s="40"/>
-      <c r="P14" s="40"/>
-      <c r="Q14" s="40"/>
-    </row>
-    <row r="15" spans="1:17" s="23" customFormat="1" ht="87" customHeight="1">
-      <c r="A15" s="40" t="s">
+      <c r="I15" s="40"/>
+      <c r="J15" s="46" t="s">
+        <v>163</v>
+      </c>
+      <c r="K15" s="50" t="s">
+        <v>160</v>
+      </c>
+      <c r="L15" s="41"/>
+      <c r="M15" s="41"/>
+      <c r="N15" s="41"/>
+      <c r="O15" s="43"/>
+      <c r="P15" s="39"/>
+      <c r="Q15" s="39"/>
+      <c r="R15" s="39" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" s="23" customFormat="1" ht="87" customHeight="1">
+      <c r="A16" s="39" t="s">
         <v>96</v>
       </c>
-      <c r="B15" s="45" t="s">
+      <c r="B16" s="41" t="s">
         <v>42</v>
       </c>
-      <c r="C15" s="45" t="s">
+      <c r="C16" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="D15" s="45" t="s">
+      <c r="D16" s="41" t="s">
         <v>41</v>
       </c>
-      <c r="E15" s="40"/>
-      <c r="F15" s="42"/>
-      <c r="G15" s="41" t="s">
-        <v>4</v>
-      </c>
-      <c r="H15" s="40" t="s">
+      <c r="E16" s="39"/>
+      <c r="F16" s="56"/>
+      <c r="G16" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="H16" s="50" t="s">
         <v>122</v>
       </c>
-      <c r="I15" s="40"/>
-      <c r="J15" s="40"/>
-      <c r="K15" s="45"/>
-      <c r="L15" s="40"/>
-      <c r="M15" s="40"/>
-      <c r="N15" s="40"/>
-      <c r="O15" s="40"/>
-      <c r="P15" s="40"/>
-      <c r="Q15" s="40"/>
-    </row>
-    <row r="16" spans="1:17" s="23" customFormat="1" ht="87" customHeight="1">
-      <c r="A16" s="40" t="s">
+      <c r="I16" s="39"/>
+      <c r="J16" s="46" t="s">
+        <v>164</v>
+      </c>
+      <c r="K16" s="49" t="s">
+        <v>160</v>
+      </c>
+      <c r="L16" s="39"/>
+      <c r="M16" s="39"/>
+      <c r="N16" s="39"/>
+      <c r="O16" s="43"/>
+      <c r="P16" s="39"/>
+      <c r="Q16" s="39"/>
+      <c r="R16" s="39" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" s="23" customFormat="1" ht="87" customHeight="1">
+      <c r="A17" s="39" t="s">
         <v>97</v>
       </c>
-      <c r="B16" s="45" t="s">
+      <c r="B17" s="41" t="s">
         <v>40</v>
       </c>
-      <c r="C16" s="45" t="s">
+      <c r="C17" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="D16" s="45" t="s">
+      <c r="D17" s="41" t="s">
         <v>39</v>
       </c>
-      <c r="E16" s="40"/>
-      <c r="F16" s="40"/>
-      <c r="G16" s="41" t="s">
-        <v>4</v>
-      </c>
-      <c r="H16" s="43" t="s">
+      <c r="E17" s="39"/>
+      <c r="F17" s="39"/>
+      <c r="G17" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="H17" s="55" t="s">
         <v>123</v>
       </c>
-      <c r="I16" s="43"/>
-      <c r="J16" s="40"/>
-      <c r="K16" s="45"/>
-      <c r="L16" s="40"/>
-      <c r="M16" s="40"/>
-      <c r="N16" s="40"/>
-      <c r="O16" s="40"/>
-      <c r="P16" s="40"/>
-      <c r="Q16" s="40"/>
-    </row>
-    <row r="17" spans="1:17" s="23" customFormat="1" ht="87" customHeight="1">
-      <c r="A17" s="40" t="s">
+      <c r="I17" s="40"/>
+      <c r="J17" s="46" t="s">
+        <v>165</v>
+      </c>
+      <c r="K17" s="49" t="s">
+        <v>160</v>
+      </c>
+      <c r="L17" s="39"/>
+      <c r="M17" s="39"/>
+      <c r="N17" s="39"/>
+      <c r="O17" s="43"/>
+      <c r="P17" s="39"/>
+      <c r="Q17" s="39"/>
+      <c r="R17" s="39" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="18" spans="1:18" s="23" customFormat="1" ht="87" customHeight="1">
+      <c r="A18" s="39" t="s">
         <v>98</v>
       </c>
-      <c r="B17" s="45" t="s">
+      <c r="B18" s="41" t="s">
         <v>38</v>
       </c>
-      <c r="C17" s="45" t="s">
+      <c r="C18" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="D17" s="45" t="s">
+      <c r="D18" s="41" t="s">
         <v>37</v>
       </c>
-      <c r="E17" s="40"/>
-      <c r="F17" s="40"/>
-      <c r="G17" s="41" t="s">
-        <v>4</v>
-      </c>
-      <c r="H17" s="43" t="s">
+      <c r="E18" s="39"/>
+      <c r="F18" s="39"/>
+      <c r="G18" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="H18" s="55" t="s">
         <v>123</v>
       </c>
-      <c r="I17" s="43"/>
-      <c r="J17" s="40"/>
-      <c r="K17" s="45"/>
-      <c r="L17" s="40"/>
-      <c r="M17" s="40"/>
-      <c r="N17" s="40"/>
-      <c r="O17" s="40"/>
-      <c r="P17" s="40"/>
-      <c r="Q17" s="40"/>
-    </row>
-    <row r="18" spans="1:17" s="23" customFormat="1" ht="87" customHeight="1">
-      <c r="A18" s="40" t="s">
+      <c r="I18" s="40"/>
+      <c r="J18" s="46" t="s">
+        <v>165</v>
+      </c>
+      <c r="K18" s="49" t="s">
+        <v>160</v>
+      </c>
+      <c r="L18" s="39"/>
+      <c r="M18" s="39"/>
+      <c r="N18" s="39"/>
+      <c r="O18" s="43"/>
+      <c r="P18" s="39"/>
+      <c r="Q18" s="39"/>
+      <c r="R18" s="39" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" s="83" customFormat="1" ht="87" customHeight="1">
+      <c r="A19" s="76" t="s">
         <v>99</v>
       </c>
-      <c r="B18" s="45" t="s">
+      <c r="B19" s="77" t="s">
         <v>36</v>
       </c>
-      <c r="C18" s="45" t="s">
+      <c r="C19" s="77" t="s">
         <v>7</v>
       </c>
-      <c r="D18" s="45" t="s">
+      <c r="D19" s="77" t="s">
         <v>35</v>
       </c>
-      <c r="E18" s="40"/>
-      <c r="F18" s="40"/>
-      <c r="G18" s="41" t="s">
-        <v>4</v>
-      </c>
-      <c r="H18" s="43" t="s">
+      <c r="E19" s="76"/>
+      <c r="F19" s="76"/>
+      <c r="G19" s="79" t="s">
+        <v>4</v>
+      </c>
+      <c r="H19" s="80" t="s">
         <v>123</v>
       </c>
-      <c r="I18" s="43"/>
-      <c r="J18" s="40"/>
-      <c r="K18" s="45"/>
-      <c r="L18" s="40"/>
-      <c r="M18" s="40"/>
-      <c r="N18" s="40"/>
-      <c r="O18" s="40"/>
-      <c r="P18" s="40"/>
-      <c r="Q18" s="40"/>
-    </row>
-    <row r="19" spans="1:17" s="23" customFormat="1" ht="87" customHeight="1">
-      <c r="A19" s="40" t="s">
+      <c r="I19" s="78"/>
+      <c r="J19" s="81" t="s">
+        <v>165</v>
+      </c>
+      <c r="K19" s="85" t="s">
+        <v>160</v>
+      </c>
+      <c r="L19" s="76"/>
+      <c r="M19" s="76"/>
+      <c r="N19" s="76"/>
+      <c r="P19" s="76"/>
+      <c r="Q19" s="76"/>
+      <c r="R19" s="76" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="20" spans="1:18" s="23" customFormat="1" ht="87" customHeight="1">
+      <c r="A20" s="39" t="s">
         <v>100</v>
       </c>
-      <c r="B19" s="45" t="s">
+      <c r="B20" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="C19" s="45" t="s">
+      <c r="C20" s="41" t="s">
         <v>33</v>
       </c>
-      <c r="D19" s="45" t="s">
+      <c r="D20" s="41" t="s">
         <v>32</v>
       </c>
-      <c r="E19" s="40"/>
-      <c r="F19" s="42"/>
-      <c r="G19" s="41" t="s">
-        <v>4</v>
-      </c>
-      <c r="H19" s="43" t="s">
+      <c r="E20" s="39"/>
+      <c r="F20" s="56"/>
+      <c r="G20" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="H20" s="55" t="s">
         <v>124</v>
       </c>
-      <c r="I19" s="43"/>
-      <c r="J19" s="40"/>
-      <c r="K19" s="45"/>
-      <c r="L19" s="40"/>
-      <c r="M19" s="40"/>
-      <c r="N19" s="40"/>
-      <c r="O19" s="40"/>
-      <c r="P19" s="40"/>
-      <c r="Q19" s="40"/>
-    </row>
-    <row r="20" spans="1:17" s="23" customFormat="1" ht="87" customHeight="1">
-      <c r="A20" s="40" t="s">
+      <c r="I20" s="40"/>
+      <c r="J20" s="46"/>
+      <c r="K20" s="49" t="s">
+        <v>34</v>
+      </c>
+      <c r="L20" s="41" t="s">
+        <v>34</v>
+      </c>
+      <c r="M20" s="41" t="s">
+        <v>33</v>
+      </c>
+      <c r="N20" s="41" t="s">
+        <v>166</v>
+      </c>
+      <c r="O20" s="43"/>
+      <c r="P20" s="56"/>
+      <c r="Q20" s="53" t="s">
+        <v>144</v>
+      </c>
+      <c r="R20" s="39" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="21" spans="1:18" s="23" customFormat="1" ht="87" customHeight="1">
+      <c r="A21" s="39" t="s">
         <v>101</v>
       </c>
-      <c r="B20" s="45" t="s">
+      <c r="B21" s="41" t="s">
         <v>31</v>
       </c>
-      <c r="C20" s="45" t="s">
+      <c r="C21" s="41" t="s">
         <v>30</v>
       </c>
-      <c r="D20" s="45" t="s">
+      <c r="D21" s="41" t="s">
         <v>29</v>
       </c>
-      <c r="E20" s="40"/>
-      <c r="F20" s="42"/>
-      <c r="G20" s="41" t="s">
-        <v>4</v>
-      </c>
-      <c r="H20" s="40" t="s">
+      <c r="E21" s="39"/>
+      <c r="F21" s="56"/>
+      <c r="G21" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="H21" s="50" t="s">
         <v>125</v>
       </c>
-      <c r="I20" s="40"/>
-      <c r="J20" s="40"/>
-      <c r="K20" s="45"/>
-      <c r="L20" s="40"/>
-      <c r="M20" s="40"/>
-      <c r="N20" s="40"/>
-      <c r="O20" s="40"/>
-      <c r="P20" s="40"/>
-      <c r="Q20" s="40"/>
-    </row>
-    <row r="21" spans="1:17" s="23" customFormat="1" ht="87" customHeight="1">
-      <c r="A21" s="40" t="s">
+      <c r="I21" s="39"/>
+      <c r="J21" s="46" t="s">
+        <v>165</v>
+      </c>
+      <c r="K21" s="49" t="s">
+        <v>160</v>
+      </c>
+      <c r="L21" s="39"/>
+      <c r="M21" s="39"/>
+      <c r="N21" s="39"/>
+      <c r="O21" s="43"/>
+      <c r="P21" s="39"/>
+      <c r="Q21" s="39"/>
+      <c r="R21" s="39" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="22" spans="1:18" s="23" customFormat="1" ht="87" customHeight="1">
+      <c r="A22" s="39" t="s">
         <v>102</v>
       </c>
-      <c r="B21" s="45" t="s">
+      <c r="B22" s="41" t="s">
         <v>28</v>
       </c>
-      <c r="C21" s="45" t="s">
+      <c r="C22" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="D21" s="45" t="s">
+      <c r="D22" s="41" t="s">
         <v>27</v>
       </c>
-      <c r="E21" s="40"/>
-      <c r="F21" s="40"/>
-      <c r="G21" s="41" t="s">
-        <v>4</v>
-      </c>
-      <c r="H21" s="40"/>
-      <c r="I21" s="40"/>
-      <c r="J21" s="40"/>
-      <c r="K21" s="45"/>
-      <c r="L21" s="40"/>
-      <c r="M21" s="40"/>
-      <c r="N21" s="40"/>
-      <c r="O21" s="40"/>
-      <c r="P21" s="40"/>
-      <c r="Q21" s="40"/>
-    </row>
-    <row r="22" spans="1:17" s="23" customFormat="1" ht="87" customHeight="1">
-      <c r="A22" s="40" t="s">
+      <c r="E22" s="39"/>
+      <c r="F22" s="39"/>
+      <c r="G22" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="H22" s="50"/>
+      <c r="I22" s="39"/>
+      <c r="J22" s="46" t="s">
+        <v>165</v>
+      </c>
+      <c r="K22" s="49" t="s">
+        <v>160</v>
+      </c>
+      <c r="L22" s="39"/>
+      <c r="M22" s="39"/>
+      <c r="N22" s="39"/>
+      <c r="O22" s="43"/>
+      <c r="P22" s="39"/>
+      <c r="Q22" s="39"/>
+      <c r="R22" s="39" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="23" spans="1:18" s="23" customFormat="1" ht="87" customHeight="1">
+      <c r="A23" s="39" t="s">
         <v>103</v>
       </c>
-      <c r="B22" s="45" t="s">
+      <c r="B23" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="C22" s="45" t="s">
+      <c r="C23" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="D22" s="45" t="s">
+      <c r="D23" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="E22" s="40"/>
-      <c r="F22" s="40"/>
-      <c r="G22" s="41" t="s">
-        <v>4</v>
-      </c>
-      <c r="H22" s="40"/>
-      <c r="I22" s="40"/>
-      <c r="J22" s="40"/>
-      <c r="K22" s="45"/>
-      <c r="L22" s="40"/>
-      <c r="M22" s="40"/>
-      <c r="N22" s="40"/>
-      <c r="O22" s="40"/>
-      <c r="P22" s="40"/>
-      <c r="Q22" s="40"/>
-    </row>
-    <row r="23" spans="1:17" s="23" customFormat="1" ht="87" customHeight="1">
-      <c r="A23" s="40" t="s">
+      <c r="E23" s="39"/>
+      <c r="F23" s="39"/>
+      <c r="G23" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="H23" s="50"/>
+      <c r="I23" s="39"/>
+      <c r="J23" s="46" t="s">
+        <v>165</v>
+      </c>
+      <c r="K23" s="49" t="s">
+        <v>160</v>
+      </c>
+      <c r="L23" s="39"/>
+      <c r="M23" s="39"/>
+      <c r="N23" s="39"/>
+      <c r="O23" s="43"/>
+      <c r="P23" s="39"/>
+      <c r="Q23" s="39"/>
+      <c r="R23" s="39" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" s="23" customFormat="1" ht="87" customHeight="1">
+      <c r="A24" s="76" t="s">
         <v>106</v>
       </c>
-      <c r="B23" s="45" t="s">
+      <c r="B24" s="77" t="s">
         <v>24</v>
       </c>
-      <c r="C23" s="45" t="s">
+      <c r="C24" s="77" t="s">
         <v>19</v>
       </c>
-      <c r="D23" s="45" t="s">
+      <c r="D24" s="77" t="s">
         <v>23</v>
       </c>
-      <c r="E23" s="40"/>
-      <c r="F23" s="40"/>
-      <c r="G23" s="41" t="s">
-        <v>4</v>
-      </c>
-      <c r="H23" s="40"/>
-      <c r="I23" s="40"/>
-      <c r="J23" s="40"/>
-      <c r="K23" s="45"/>
-      <c r="L23" s="40"/>
-      <c r="M23" s="40"/>
-      <c r="N23" s="40"/>
-      <c r="O23" s="40"/>
-      <c r="P23" s="40"/>
-      <c r="Q23" s="40"/>
-    </row>
-    <row r="24" spans="1:17" s="23" customFormat="1" ht="87" customHeight="1">
-      <c r="A24" s="40" t="s">
+      <c r="E24" s="39"/>
+      <c r="F24" s="76"/>
+      <c r="G24" s="79" t="s">
+        <v>4</v>
+      </c>
+      <c r="H24" s="82"/>
+      <c r="I24" s="76"/>
+      <c r="J24" s="81" t="s">
+        <v>167</v>
+      </c>
+      <c r="K24" s="69" t="s">
+        <v>187</v>
+      </c>
+      <c r="L24" s="67"/>
+      <c r="M24" s="67"/>
+      <c r="N24" s="67"/>
+      <c r="O24" s="68"/>
+      <c r="P24" s="66"/>
+      <c r="Q24" s="79" t="s">
+        <v>4</v>
+      </c>
+      <c r="R24" s="76" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" s="23" customFormat="1" ht="87" customHeight="1">
+      <c r="A25" s="39" t="s">
         <v>104</v>
       </c>
-      <c r="B24" s="45" t="s">
+      <c r="B25" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="C24" s="45" t="s">
+      <c r="C25" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="45" t="s">
+      <c r="D25" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="E24" s="40"/>
-      <c r="F24" s="40"/>
-      <c r="G24" s="41" t="s">
-        <v>4</v>
-      </c>
-      <c r="H24" s="40"/>
-      <c r="I24" s="40"/>
-      <c r="J24" s="40"/>
-      <c r="K24" s="45"/>
-      <c r="L24" s="40"/>
-      <c r="M24" s="40"/>
-      <c r="N24" s="40"/>
-      <c r="O24" s="40"/>
-      <c r="P24" s="40"/>
-      <c r="Q24" s="40"/>
-    </row>
-    <row r="25" spans="1:17" s="23" customFormat="1" ht="87" customHeight="1">
-      <c r="A25" s="40" t="s">
+      <c r="E25" s="39"/>
+      <c r="F25" s="39"/>
+      <c r="G25" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="H25" s="50"/>
+      <c r="I25" s="39"/>
+      <c r="J25" s="46" t="s">
+        <v>165</v>
+      </c>
+      <c r="K25" s="49" t="s">
+        <v>160</v>
+      </c>
+      <c r="L25" s="39"/>
+      <c r="M25" s="39"/>
+      <c r="N25" s="39"/>
+      <c r="O25" s="43"/>
+      <c r="P25" s="39"/>
+      <c r="Q25" s="39"/>
+      <c r="R25" s="39" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" s="23" customFormat="1" ht="87" customHeight="1">
+      <c r="A26" s="39" t="s">
         <v>105</v>
       </c>
-      <c r="B25" s="45" t="s">
+      <c r="B26" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="C25" s="45" t="s">
+      <c r="C26" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="D25" s="45" t="s">
+      <c r="D26" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="E25" s="48"/>
-      <c r="F25" s="48"/>
-      <c r="G25" s="41" t="s">
-        <v>4</v>
-      </c>
-      <c r="H25" s="48"/>
-      <c r="I25" s="48"/>
-      <c r="J25" s="48"/>
-      <c r="K25" s="45"/>
-      <c r="L25" s="48"/>
-      <c r="M25" s="48"/>
-      <c r="N25" s="48"/>
-      <c r="O25" s="48"/>
-      <c r="P25" s="48"/>
-      <c r="Q25" s="48"/>
-    </row>
-    <row r="26" spans="1:17" s="23" customFormat="1" ht="87" customHeight="1">
-      <c r="A26" s="40" t="s">
+      <c r="E26" s="41"/>
+      <c r="F26" s="41"/>
+      <c r="G26" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="H26" s="49"/>
+      <c r="I26" s="41"/>
+      <c r="J26" s="46" t="s">
+        <v>165</v>
+      </c>
+      <c r="K26" s="49" t="s">
+        <v>160</v>
+      </c>
+      <c r="L26" s="41"/>
+      <c r="M26" s="41"/>
+      <c r="N26" s="41"/>
+      <c r="O26" s="43"/>
+      <c r="P26" s="41"/>
+      <c r="Q26" s="41"/>
+      <c r="R26" s="39" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" s="23" customFormat="1" ht="87" customHeight="1">
+      <c r="A27" s="76" t="s">
         <v>107</v>
       </c>
-      <c r="B26" s="45" t="s">
+      <c r="B27" s="77" t="s">
         <v>17</v>
       </c>
-      <c r="C26" s="45" t="s">
+      <c r="C27" s="77" t="s">
         <v>16</v>
       </c>
-      <c r="D26" s="45" t="s">
+      <c r="D27" s="77" t="s">
         <v>108</v>
       </c>
-      <c r="E26" s="48"/>
-      <c r="F26" s="48" t="s">
+      <c r="E27" s="41"/>
+      <c r="F27" s="77" t="s">
         <v>109</v>
       </c>
-      <c r="G26" s="41" t="s">
-        <v>4</v>
-      </c>
-      <c r="H26" s="48" t="s">
+      <c r="G27" s="79" t="s">
+        <v>4</v>
+      </c>
+      <c r="H27" s="85" t="s">
         <v>126</v>
       </c>
-      <c r="I26" s="48"/>
-      <c r="J26" s="48"/>
-      <c r="K26" s="45"/>
-      <c r="L26" s="48"/>
-      <c r="M26" s="48"/>
-      <c r="N26" s="48"/>
-      <c r="O26" s="48"/>
-      <c r="P26" s="48"/>
-      <c r="Q26" s="48"/>
-    </row>
-    <row r="27" spans="1:17" s="23" customFormat="1" ht="87" customHeight="1">
-      <c r="A27" s="40" t="s">
+      <c r="I27" s="77"/>
+      <c r="J27" s="81" t="s">
+        <v>170</v>
+      </c>
+      <c r="K27" s="85" t="s">
+        <v>168</v>
+      </c>
+      <c r="L27" s="68"/>
+      <c r="M27" s="67" t="s">
+        <v>169</v>
+      </c>
+      <c r="N27" s="67"/>
+      <c r="O27" s="68"/>
+      <c r="P27" s="67"/>
+      <c r="Q27" s="79" t="s">
+        <v>144</v>
+      </c>
+      <c r="R27" s="76" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" s="23" customFormat="1" ht="87" customHeight="1">
+      <c r="A28" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="B27" s="45" t="s">
+      <c r="B28" s="41" t="s">
         <v>14</v>
       </c>
-      <c r="C27" s="45" t="s">
+      <c r="C28" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="D27" s="45" t="s">
+      <c r="D28" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="E27" s="48"/>
-      <c r="F27" s="48"/>
-      <c r="G27" s="41" t="s">
-        <v>4</v>
-      </c>
-      <c r="H27" s="48" t="s">
+      <c r="E28" s="41"/>
+      <c r="F28" s="41"/>
+      <c r="G28" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="H28" s="49" t="s">
         <v>127</v>
       </c>
-      <c r="I27" s="48"/>
-      <c r="J27" s="45"/>
-      <c r="K27" s="45"/>
-      <c r="L27" s="48"/>
-      <c r="M27" s="48"/>
-      <c r="N27" s="48"/>
-      <c r="O27" s="48"/>
-      <c r="P27" s="48"/>
-      <c r="Q27" s="45"/>
-    </row>
-    <row r="28" spans="1:17" s="23" customFormat="1" ht="87" customHeight="1">
-      <c r="A28" s="40" t="s">
+      <c r="I28" s="41"/>
+      <c r="J28" s="46" t="s">
+        <v>171</v>
+      </c>
+      <c r="K28" s="49" t="s">
+        <v>160</v>
+      </c>
+      <c r="L28" s="41"/>
+      <c r="M28" s="41"/>
+      <c r="N28" s="41"/>
+      <c r="O28" s="43"/>
+      <c r="P28" s="41"/>
+      <c r="Q28" s="41"/>
+      <c r="R28" s="39" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="29" spans="1:18" s="23" customFormat="1" ht="87" customHeight="1">
+      <c r="A29" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="B28" s="45" t="s">
+      <c r="B29" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="C28" s="45" t="s">
+      <c r="C29" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="D28" s="45" t="s">
+      <c r="D29" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="E28" s="45"/>
-      <c r="F28" s="45"/>
-      <c r="G28" s="41" t="s">
-        <v>4</v>
-      </c>
-      <c r="H28" s="48" t="s">
+      <c r="E29" s="41"/>
+      <c r="F29" s="41"/>
+      <c r="G29" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="H29" s="49" t="s">
         <v>127</v>
       </c>
-      <c r="I28" s="48"/>
-      <c r="J28" s="45"/>
-      <c r="K28" s="45"/>
-      <c r="L28" s="45"/>
-      <c r="M28" s="45"/>
-      <c r="N28" s="45"/>
-      <c r="O28" s="45"/>
-      <c r="P28" s="45"/>
-      <c r="Q28" s="45"/>
-    </row>
-    <row r="29" spans="1:17" s="23" customFormat="1" ht="87" customHeight="1">
-      <c r="A29" s="40" t="s">
+      <c r="I29" s="41"/>
+      <c r="J29" s="46" t="s">
+        <v>171</v>
+      </c>
+      <c r="K29" s="49" t="s">
+        <v>160</v>
+      </c>
+      <c r="L29" s="41"/>
+      <c r="M29" s="41"/>
+      <c r="N29" s="41"/>
+      <c r="O29" s="43"/>
+      <c r="P29" s="41"/>
+      <c r="Q29" s="41"/>
+      <c r="R29" s="39" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="30" spans="1:18" s="23" customFormat="1" ht="87" customHeight="1">
+      <c r="A30" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="B29" s="45" t="s">
+      <c r="B30" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="C29" s="45" t="s">
+      <c r="C30" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="D29" s="45" t="s">
+      <c r="D30" s="41" t="s">
         <v>9</v>
       </c>
-      <c r="E29" s="45"/>
-      <c r="F29" s="45"/>
-      <c r="G29" s="41" t="s">
-        <v>4</v>
-      </c>
-      <c r="H29" s="48" t="s">
+      <c r="E30" s="41"/>
+      <c r="F30" s="41"/>
+      <c r="G30" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="H30" s="49" t="s">
         <v>127</v>
       </c>
-      <c r="I29" s="48"/>
-      <c r="J29" s="45"/>
-      <c r="K29" s="45"/>
-      <c r="L29" s="45"/>
-      <c r="M29" s="45"/>
-      <c r="N29" s="45"/>
-      <c r="O29" s="45"/>
-      <c r="P29" s="45"/>
-      <c r="Q29" s="45"/>
-    </row>
-    <row r="30" spans="1:17" s="23" customFormat="1" ht="87" customHeight="1">
-      <c r="A30" s="40" t="s">
+      <c r="I30" s="41"/>
+      <c r="J30" s="46" t="s">
+        <v>171</v>
+      </c>
+      <c r="K30" s="49" t="s">
+        <v>160</v>
+      </c>
+      <c r="L30" s="41"/>
+      <c r="M30" s="41"/>
+      <c r="N30" s="41"/>
+      <c r="O30" s="43"/>
+      <c r="P30" s="41"/>
+      <c r="Q30" s="41"/>
+      <c r="R30" s="39" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="31" spans="1:18" s="23" customFormat="1" ht="87" customHeight="1">
+      <c r="A31" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="B30" s="45" t="s">
+      <c r="B31" s="41" t="s">
         <v>8</v>
       </c>
-      <c r="C30" s="45" t="s">
+      <c r="C31" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="D30" s="45" t="s">
+      <c r="D31" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="E30" s="45"/>
-      <c r="F30" s="45"/>
-      <c r="G30" s="41" t="s">
-        <v>4</v>
-      </c>
-      <c r="H30" s="48" t="s">
+      <c r="E31" s="41"/>
+      <c r="F31" s="41"/>
+      <c r="G31" s="53" t="s">
+        <v>4</v>
+      </c>
+      <c r="H31" s="49" t="s">
         <v>127</v>
       </c>
-      <c r="I30" s="48"/>
-      <c r="J30" s="45"/>
-      <c r="K30" s="45"/>
-      <c r="L30" s="45"/>
-      <c r="M30" s="45"/>
-      <c r="N30" s="45"/>
-      <c r="O30" s="45"/>
-      <c r="P30" s="45"/>
-      <c r="Q30" s="45"/>
-    </row>
-    <row r="31" spans="1:17" s="23" customFormat="1" ht="87" customHeight="1">
-      <c r="A31" s="21" t="s">
+      <c r="I31" s="41"/>
+      <c r="J31" s="46" t="s">
+        <v>171</v>
+      </c>
+      <c r="K31" s="49" t="s">
+        <v>160</v>
+      </c>
+      <c r="L31" s="41"/>
+      <c r="M31" s="41"/>
+      <c r="N31" s="41"/>
+      <c r="O31" s="43"/>
+      <c r="P31" s="41"/>
+      <c r="Q31" s="41"/>
+      <c r="R31" s="39" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" s="23" customFormat="1" ht="87" customHeight="1">
+      <c r="A32" s="37" t="s">
         <v>135</v>
       </c>
-      <c r="B31" s="21"/>
-      <c r="C31" s="21"/>
-      <c r="D31" s="21"/>
-      <c r="E31" s="21"/>
-      <c r="F31" s="21"/>
-      <c r="G31" s="21"/>
-      <c r="H31" s="21"/>
-      <c r="I31" s="21"/>
-      <c r="J31" s="21"/>
-      <c r="K31" s="21"/>
-      <c r="L31" s="21"/>
-      <c r="M31" s="21"/>
-      <c r="N31" s="21"/>
-      <c r="O31" s="21"/>
-      <c r="P31" s="21"/>
-      <c r="Q31" s="21"/>
-    </row>
-    <row r="32" spans="1:17" ht="87" customHeight="1">
-      <c r="A32" s="50" t="s">
+      <c r="B32" s="37"/>
+      <c r="C32" s="37"/>
+      <c r="D32" s="37"/>
+      <c r="E32" s="37"/>
+      <c r="F32" s="37"/>
+      <c r="G32" s="57"/>
+      <c r="H32" s="58"/>
+      <c r="I32" s="37"/>
+      <c r="J32" s="57" t="s">
+        <v>191</v>
+      </c>
+      <c r="K32" s="58" t="s">
+        <v>172</v>
+      </c>
+      <c r="L32" s="37" t="s">
+        <v>188</v>
+      </c>
+      <c r="M32" s="37" t="s">
+        <v>154</v>
+      </c>
+      <c r="N32" s="37" t="s">
+        <v>189</v>
+      </c>
+      <c r="O32" s="43"/>
+      <c r="P32" s="40" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q32" s="53" t="s">
+        <v>144</v>
+      </c>
+      <c r="R32" s="39" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="33" spans="1:18" ht="87" customHeight="1">
+      <c r="A33" s="87" t="s">
         <v>136</v>
       </c>
-      <c r="B32" s="50"/>
-      <c r="C32" s="50"/>
-      <c r="D32" s="50"/>
-      <c r="E32" s="50"/>
-      <c r="F32" s="50"/>
-      <c r="G32" s="50"/>
-      <c r="H32" s="50"/>
-      <c r="I32" s="50"/>
-      <c r="J32" s="50"/>
-      <c r="K32" s="50"/>
-      <c r="L32" s="50"/>
-      <c r="M32" s="50"/>
-      <c r="N32" s="50"/>
-      <c r="O32" s="50"/>
-      <c r="P32" s="50"/>
-      <c r="Q32" s="50"/>
-    </row>
-    <row r="33" spans="1:17" ht="87" customHeight="1">
-      <c r="A33" s="50" t="s">
+      <c r="B33" s="87"/>
+      <c r="C33" s="87"/>
+      <c r="D33" s="87"/>
+      <c r="E33" s="59"/>
+      <c r="F33" s="87"/>
+      <c r="G33" s="90"/>
+      <c r="H33" s="86"/>
+      <c r="I33" s="87"/>
+      <c r="J33" s="90" t="s">
+        <v>173</v>
+      </c>
+      <c r="K33" s="86" t="s">
+        <v>192</v>
+      </c>
+      <c r="L33" s="70"/>
+      <c r="M33" s="87" t="s">
+        <v>154</v>
+      </c>
+      <c r="N33" s="70"/>
+      <c r="O33" s="71"/>
+      <c r="P33" s="70"/>
+      <c r="Q33" s="79" t="s">
+        <v>144</v>
+      </c>
+      <c r="R33" s="76" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" ht="87" customHeight="1">
+      <c r="A34" s="59" t="s">
         <v>138</v>
       </c>
-      <c r="B33" s="50"/>
-      <c r="C33" s="50"/>
-      <c r="D33" s="50"/>
-      <c r="E33" s="50"/>
-      <c r="F33" s="50"/>
-      <c r="G33" s="50"/>
-      <c r="H33" s="50"/>
-      <c r="I33" s="50"/>
-      <c r="J33" s="50"/>
-      <c r="K33" s="50"/>
-      <c r="L33" s="50"/>
-      <c r="M33" s="50"/>
-      <c r="N33" s="50"/>
-      <c r="O33" s="50"/>
-      <c r="P33" s="50"/>
-      <c r="Q33" s="50"/>
-    </row>
-    <row r="34" spans="1:17" ht="87" customHeight="1">
-      <c r="A34" s="50" t="s">
+      <c r="B34" s="59"/>
+      <c r="C34" s="59"/>
+      <c r="D34" s="59"/>
+      <c r="E34" s="59"/>
+      <c r="F34" s="59"/>
+      <c r="G34" s="60"/>
+      <c r="H34" s="61"/>
+      <c r="I34" s="59"/>
+      <c r="J34" s="60" t="s">
+        <v>174</v>
+      </c>
+      <c r="K34" s="49" t="s">
+        <v>160</v>
+      </c>
+      <c r="L34" s="59"/>
+      <c r="M34" s="59"/>
+      <c r="N34" s="59"/>
+      <c r="O34" s="64"/>
+      <c r="P34" s="59"/>
+      <c r="Q34" s="59"/>
+      <c r="R34" s="39" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="35" spans="1:18" ht="87" customHeight="1">
+      <c r="A35" s="59" t="s">
         <v>137</v>
       </c>
-      <c r="B34" s="50"/>
-      <c r="C34" s="50"/>
-      <c r="D34" s="50"/>
-      <c r="E34" s="50"/>
-      <c r="F34" s="50"/>
-      <c r="G34" s="50"/>
-      <c r="H34" s="50"/>
-      <c r="I34" s="50"/>
-      <c r="J34" s="50"/>
-      <c r="K34" s="50"/>
-      <c r="L34" s="50"/>
-      <c r="M34" s="50"/>
-      <c r="N34" s="50"/>
-      <c r="O34" s="50"/>
-      <c r="P34" s="50"/>
-      <c r="Q34" s="50"/>
-    </row>
-    <row r="35" spans="1:17" ht="87" customHeight="1">
-      <c r="A35" s="50" t="s">
+      <c r="B35" s="59"/>
+      <c r="C35" s="59"/>
+      <c r="D35" s="59"/>
+      <c r="E35" s="59"/>
+      <c r="F35" s="59"/>
+      <c r="G35" s="60"/>
+      <c r="H35" s="61"/>
+      <c r="I35" s="59"/>
+      <c r="J35" s="60" t="s">
+        <v>175</v>
+      </c>
+      <c r="K35" s="49" t="s">
+        <v>160</v>
+      </c>
+      <c r="L35" s="59"/>
+      <c r="M35" s="59"/>
+      <c r="N35" s="59"/>
+      <c r="O35" s="64"/>
+      <c r="P35" s="59"/>
+      <c r="Q35" s="59"/>
+      <c r="R35" s="39" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="36" spans="1:18" ht="87" customHeight="1">
+      <c r="A36" s="59" t="s">
         <v>139</v>
       </c>
-      <c r="B35" s="50"/>
-      <c r="C35" s="50"/>
-      <c r="D35" s="50"/>
-      <c r="E35" s="50"/>
-      <c r="F35" s="50"/>
-      <c r="G35" s="50"/>
-      <c r="H35" s="50"/>
-      <c r="I35" s="50"/>
-      <c r="J35" s="50"/>
-      <c r="K35" s="50"/>
-      <c r="L35" s="50"/>
-      <c r="M35" s="50"/>
-      <c r="N35" s="50"/>
-      <c r="O35" s="50"/>
-      <c r="P35" s="50"/>
-      <c r="Q35" s="50"/>
+      <c r="B36" s="59"/>
+      <c r="C36" s="59"/>
+      <c r="D36" s="59"/>
+      <c r="E36" s="59"/>
+      <c r="F36" s="59"/>
+      <c r="G36" s="60"/>
+      <c r="H36" s="61"/>
+      <c r="I36" s="59"/>
+      <c r="J36" s="60" t="s">
+        <v>193</v>
+      </c>
+      <c r="K36" s="49" t="s">
+        <v>160</v>
+      </c>
+      <c r="L36" s="59"/>
+      <c r="M36" s="59"/>
+      <c r="N36" s="59"/>
+      <c r="O36" s="64"/>
+      <c r="P36" s="59"/>
+      <c r="Q36" s="59"/>
+      <c r="R36" s="39" t="s">
+        <v>131</v>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A2:R36" xr:uid="{D536427B-83A6-4707-8C45-6BB4F1975BE7}"/>
   <mergeCells count="3">
     <mergeCell ref="B1:G1"/>
-    <mergeCell ref="K1:P1"/>
+    <mergeCell ref="K1:Q1"/>
     <mergeCell ref="H1:J1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
